--- a/Utilities/titles/VariableListing.xlsx
+++ b/Utilities/titles/VariableListing.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Work profile\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Work profile\Documents\GitHub\FTT_StandAlone\Utilities\titles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B6FBE3B-9D55-418B-9038-FD51099BA3CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{820AC22B-2FED-4142-995A-27D7F6AF9D4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="10305" windowHeight="17400" xr2:uid="{3966A5EA-18B5-40FC-82B6-8DC341B5B05B}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" xr2:uid="{3966A5EA-18B5-40FC-82B6-8DC341B5B05B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -3421,7 +3421,7 @@
         <v>9</v>
       </c>
       <c r="K14">
-        <v>2001</v>
+        <v>2010</v>
       </c>
       <c r="L14" t="s">
         <v>9</v>
@@ -6085,7 +6085,7 @@
         <v>9</v>
       </c>
       <c r="K81">
-        <v>2001</v>
+        <v>2010</v>
       </c>
       <c r="L81" t="s">
         <v>9</v>

--- a/Utilities/titles/VariableListing.xlsx
+++ b/Utilities/titles/VariableListing.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Work profile\Documents\GitHub\FTT_StandAlone\Utilities\titles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{820AC22B-2FED-4142-995A-27D7F6AF9D4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D02C101A-197E-421E-B5BF-F6988C5F41F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" xr2:uid="{3966A5EA-18B5-40FC-82B6-8DC341B5B05B}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$N$368</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$N$370</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3747" uniqueCount="807">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3767" uniqueCount="811">
   <si>
     <t>Variable name</t>
   </si>
@@ -2458,6 +2458,18 @@
   </si>
   <si>
     <t>FTT-Transport levelised costs with taxes</t>
+  </si>
+  <si>
+    <t>MCTG</t>
+  </si>
+  <si>
+    <t>FTT:Power Gross curtailment rate by technology (-)</t>
+  </si>
+  <si>
+    <t>MKLB</t>
+  </si>
+  <si>
+    <t>Capacity by load band</t>
   </si>
 </sst>
 </file>
@@ -2832,7 +2844,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5694E675-77F6-4F54-A793-A54451BF0049}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:N368"/>
+  <dimension ref="A1:N370"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14" bestFit="1" customWidth="1"/>
@@ -5360,19 +5372,19 @@
     </row>
     <row r="64" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
-        <v>787</v>
+        <v>809</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>788</v>
+        <v>810</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="D64" s="2" t="s">
         <v>29</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>41</v>
+        <v>200</v>
       </c>
       <c r="F64" s="2" t="s">
         <v>17</v>
@@ -5390,9 +5402,11 @@
         <v>9</v>
       </c>
       <c r="K64" s="2">
-        <v>2010</v>
-      </c>
-      <c r="L64" s="2"/>
+        <v>2001</v>
+      </c>
+      <c r="L64" s="2" t="s">
+        <v>9</v>
+      </c>
       <c r="M64" s="2"/>
       <c r="N64" s="2" t="s">
         <v>229</v>
@@ -5400,19 +5414,19 @@
     </row>
     <row r="65" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
-        <v>62</v>
+        <v>787</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>191</v>
+        <v>6</v>
       </c>
       <c r="D65" s="2" t="s">
         <v>29</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>199</v>
+        <v>41</v>
       </c>
       <c r="F65" s="2" t="s">
         <v>17</v>
@@ -5439,67 +5453,66 @@
       </c>
     </row>
     <row r="66" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A66" t="s">
-        <v>76</v>
-      </c>
-      <c r="B66" t="s">
-        <v>179</v>
-      </c>
-      <c r="C66" t="s">
-        <v>187</v>
-      </c>
-      <c r="D66" t="s">
-        <v>17</v>
-      </c>
-      <c r="E66" t="s">
-        <v>11</v>
-      </c>
-      <c r="F66" t="s">
+      <c r="A66" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>789</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="D66" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E66" s="2" t="s">
         <v>199</v>
       </c>
-      <c r="G66" t="s">
-        <v>17</v>
-      </c>
-      <c r="H66" t="s">
+      <c r="F66" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G66" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H66" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="I66" t="s">
-        <v>9</v>
-      </c>
-      <c r="J66" t="s">
-        <v>9</v>
-      </c>
-      <c r="K66">
-        <v>2001</v>
-      </c>
-      <c r="L66" t="s">
-        <v>9</v>
-      </c>
-      <c r="N66" t="s">
+      <c r="I66" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="J66" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="K66" s="2">
+        <v>2010</v>
+      </c>
+      <c r="L66" s="2"/>
+      <c r="M66" s="2"/>
+      <c r="N66" s="2" t="s">
         <v>229</v>
       </c>
     </row>
     <row r="67" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B67" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="C67" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D67" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="E67" t="s">
-        <v>197</v>
+        <v>11</v>
       </c>
       <c r="F67" t="s">
-        <v>17</v>
+        <v>199</v>
       </c>
       <c r="G67" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="H67" t="s">
         <v>31</v>
@@ -5522,19 +5535,19 @@
     </row>
     <row r="68" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>45</v>
+        <v>74</v>
       </c>
       <c r="B68" t="s">
-        <v>46</v>
+        <v>177</v>
       </c>
       <c r="C68" t="s">
-        <v>6</v>
+        <v>188</v>
       </c>
       <c r="D68" t="s">
         <v>29</v>
       </c>
       <c r="E68" t="s">
-        <v>11</v>
+        <v>197</v>
       </c>
       <c r="F68" t="s">
         <v>17</v>
@@ -5563,10 +5576,10 @@
     </row>
     <row r="69" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>77</v>
+        <v>45</v>
       </c>
       <c r="B69" t="s">
-        <v>180</v>
+        <v>46</v>
       </c>
       <c r="C69" t="s">
         <v>6</v>
@@ -5575,7 +5588,7 @@
         <v>29</v>
       </c>
       <c r="E69" t="s">
-        <v>199</v>
+        <v>11</v>
       </c>
       <c r="F69" t="s">
         <v>17</v>
@@ -5604,19 +5617,19 @@
     </row>
     <row r="70" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="B70" t="s">
-        <v>134</v>
+        <v>180</v>
       </c>
       <c r="C70" t="s">
-        <v>35</v>
+        <v>6</v>
       </c>
       <c r="D70" t="s">
         <v>29</v>
       </c>
       <c r="E70" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F70" t="s">
         <v>17</v>
@@ -5645,19 +5658,19 @@
     </row>
     <row r="71" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>231</v>
+        <v>87</v>
       </c>
       <c r="B71" t="s">
-        <v>240</v>
+        <v>134</v>
       </c>
       <c r="C71" t="s">
-        <v>188</v>
+        <v>35</v>
       </c>
       <c r="D71" t="s">
         <v>29</v>
       </c>
       <c r="E71" t="s">
-        <v>11</v>
+        <v>200</v>
       </c>
       <c r="F71" t="s">
         <v>17</v>
@@ -5675,10 +5688,10 @@
         <v>9</v>
       </c>
       <c r="K71">
-        <v>2010</v>
+        <v>2001</v>
       </c>
       <c r="L71" t="s">
-        <v>224</v>
+        <v>9</v>
       </c>
       <c r="N71" t="s">
         <v>229</v>
@@ -5686,10 +5699,10 @@
     </row>
     <row r="72" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>97</v>
+        <v>231</v>
       </c>
       <c r="B72" t="s">
-        <v>124</v>
+        <v>240</v>
       </c>
       <c r="C72" t="s">
         <v>188</v>
@@ -5719,7 +5732,7 @@
         <v>2010</v>
       </c>
       <c r="L72" t="s">
-        <v>9</v>
+        <v>224</v>
       </c>
       <c r="N72" t="s">
         <v>229</v>
@@ -5727,16 +5740,16 @@
     </row>
     <row r="73" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>42</v>
+        <v>97</v>
       </c>
       <c r="B73" t="s">
-        <v>43</v>
+        <v>124</v>
       </c>
       <c r="C73" t="s">
-        <v>16</v>
+        <v>188</v>
       </c>
       <c r="D73" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="E73" t="s">
         <v>11</v>
@@ -5757,7 +5770,7 @@
         <v>9</v>
       </c>
       <c r="K73">
-        <v>2001</v>
+        <v>2010</v>
       </c>
       <c r="L73" t="s">
         <v>9</v>
@@ -5768,16 +5781,16 @@
     </row>
     <row r="74" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="B74" t="s">
-        <v>158</v>
+        <v>43</v>
       </c>
       <c r="C74" t="s">
-        <v>159</v>
+        <v>16</v>
       </c>
       <c r="D74" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="E74" t="s">
         <v>11</v>
@@ -5794,8 +5807,8 @@
       <c r="I74" t="s">
         <v>9</v>
       </c>
-      <c r="J74">
-        <v>2016</v>
+      <c r="J74" t="s">
+        <v>9</v>
       </c>
       <c r="K74">
         <v>2001</v>
@@ -5809,13 +5822,13 @@
     </row>
     <row r="75" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>202</v>
+        <v>39</v>
       </c>
       <c r="B75" t="s">
-        <v>203</v>
+        <v>158</v>
       </c>
       <c r="C75" t="s">
-        <v>187</v>
+        <v>159</v>
       </c>
       <c r="D75" t="s">
         <v>29</v>
@@ -5835,8 +5848,8 @@
       <c r="I75" t="s">
         <v>9</v>
       </c>
-      <c r="J75" t="s">
-        <v>9</v>
+      <c r="J75">
+        <v>2016</v>
       </c>
       <c r="K75">
         <v>2001</v>
@@ -5850,13 +5863,13 @@
     </row>
     <row r="76" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>37</v>
+        <v>202</v>
       </c>
       <c r="B76" t="s">
-        <v>38</v>
+        <v>203</v>
       </c>
       <c r="C76" t="s">
-        <v>16</v>
+        <v>187</v>
       </c>
       <c r="D76" t="s">
         <v>29</v>
@@ -5876,8 +5889,8 @@
       <c r="I76" t="s">
         <v>9</v>
       </c>
-      <c r="J76">
-        <v>2016</v>
+      <c r="J76" t="s">
+        <v>9</v>
       </c>
       <c r="K76">
         <v>2001</v>
@@ -5891,19 +5904,19 @@
     </row>
     <row r="77" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>61</v>
+        <v>37</v>
       </c>
       <c r="B77" t="s">
-        <v>163</v>
+        <v>38</v>
       </c>
       <c r="C77" t="s">
-        <v>190</v>
+        <v>16</v>
       </c>
       <c r="D77" t="s">
         <v>29</v>
       </c>
       <c r="E77" t="s">
-        <v>199</v>
+        <v>11</v>
       </c>
       <c r="F77" t="s">
         <v>17</v>
@@ -5917,8 +5930,8 @@
       <c r="I77" t="s">
         <v>9</v>
       </c>
-      <c r="J77" t="s">
-        <v>9</v>
+      <c r="J77">
+        <v>2016</v>
       </c>
       <c r="K77">
         <v>2001</v>
@@ -5932,19 +5945,19 @@
     </row>
     <row r="78" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>230</v>
+        <v>61</v>
       </c>
       <c r="B78" t="s">
-        <v>241</v>
+        <v>163</v>
       </c>
       <c r="C78" t="s">
-        <v>159</v>
+        <v>190</v>
       </c>
       <c r="D78" t="s">
         <v>29</v>
       </c>
       <c r="E78" t="s">
-        <v>11</v>
+        <v>199</v>
       </c>
       <c r="F78" t="s">
         <v>17</v>
@@ -5962,10 +5975,10 @@
         <v>9</v>
       </c>
       <c r="K78">
-        <v>2010</v>
+        <v>2001</v>
       </c>
       <c r="L78" t="s">
-        <v>224</v>
+        <v>9</v>
       </c>
       <c r="N78" t="s">
         <v>229</v>
@@ -5973,10 +5986,10 @@
     </row>
     <row r="79" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>49</v>
+        <v>230</v>
       </c>
       <c r="B79" t="s">
-        <v>144</v>
+        <v>241</v>
       </c>
       <c r="C79" t="s">
         <v>159</v>
@@ -6003,10 +6016,10 @@
         <v>9</v>
       </c>
       <c r="K79">
-        <v>2001</v>
+        <v>2010</v>
       </c>
       <c r="L79" t="s">
-        <v>9</v>
+        <v>224</v>
       </c>
       <c r="N79" t="s">
         <v>229</v>
@@ -6014,13 +6027,13 @@
     </row>
     <row r="80" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>233</v>
+        <v>49</v>
       </c>
       <c r="B80" t="s">
-        <v>244</v>
+        <v>144</v>
       </c>
       <c r="C80" t="s">
-        <v>16</v>
+        <v>159</v>
       </c>
       <c r="D80" t="s">
         <v>29</v>
@@ -6044,10 +6057,10 @@
         <v>9</v>
       </c>
       <c r="K80">
-        <v>2010</v>
+        <v>2001</v>
       </c>
       <c r="L80" t="s">
-        <v>224</v>
+        <v>9</v>
       </c>
       <c r="N80" t="s">
         <v>229</v>
@@ -6055,10 +6068,10 @@
     </row>
     <row r="81" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>27</v>
+        <v>233</v>
       </c>
       <c r="B81" t="s">
-        <v>28</v>
+        <v>244</v>
       </c>
       <c r="C81" t="s">
         <v>16</v>
@@ -6088,10 +6101,7 @@
         <v>2010</v>
       </c>
       <c r="L81" t="s">
-        <v>9</v>
-      </c>
-      <c r="M81" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="N81" t="s">
         <v>229</v>
@@ -6099,10 +6109,10 @@
     </row>
     <row r="82" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="B82" t="s">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="C82" t="s">
         <v>16</v>
@@ -6125,14 +6135,17 @@
       <c r="I82" t="s">
         <v>9</v>
       </c>
-      <c r="J82">
-        <v>2016</v>
+      <c r="J82" t="s">
+        <v>9</v>
       </c>
       <c r="K82">
-        <v>2001</v>
+        <v>2010</v>
       </c>
       <c r="L82" t="s">
         <v>9</v>
+      </c>
+      <c r="M82" t="s">
+        <v>229</v>
       </c>
       <c r="N82" t="s">
         <v>229</v>
@@ -6140,13 +6153,13 @@
     </row>
     <row r="83" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>232</v>
+        <v>40</v>
       </c>
       <c r="B83" t="s">
-        <v>243</v>
+        <v>44</v>
       </c>
       <c r="C83" t="s">
-        <v>35</v>
+        <v>16</v>
       </c>
       <c r="D83" t="s">
         <v>29</v>
@@ -6166,14 +6179,14 @@
       <c r="I83" t="s">
         <v>9</v>
       </c>
-      <c r="J83" t="s">
-        <v>9</v>
+      <c r="J83">
+        <v>2016</v>
       </c>
       <c r="K83">
-        <v>2010</v>
+        <v>2001</v>
       </c>
       <c r="L83" t="s">
-        <v>224</v>
+        <v>9</v>
       </c>
       <c r="N83" t="s">
         <v>229</v>
@@ -6181,10 +6194,10 @@
     </row>
     <row r="84" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>30</v>
+        <v>232</v>
       </c>
       <c r="B84" t="s">
-        <v>34</v>
+        <v>243</v>
       </c>
       <c r="C84" t="s">
         <v>35</v>
@@ -6207,17 +6220,14 @@
       <c r="I84" t="s">
         <v>9</v>
       </c>
-      <c r="J84">
-        <v>2018</v>
+      <c r="J84" t="s">
+        <v>9</v>
       </c>
       <c r="K84">
-        <v>2001</v>
+        <v>2010</v>
       </c>
       <c r="L84" t="s">
-        <v>9</v>
-      </c>
-      <c r="M84" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="N84" t="s">
         <v>229</v>
@@ -6225,13 +6235,13 @@
     </row>
     <row r="85" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="B85" t="s">
-        <v>162</v>
+        <v>34</v>
       </c>
       <c r="C85" t="s">
-        <v>193</v>
+        <v>35</v>
       </c>
       <c r="D85" t="s">
         <v>29</v>
@@ -6251,8 +6261,8 @@
       <c r="I85" t="s">
         <v>9</v>
       </c>
-      <c r="J85" t="s">
-        <v>9</v>
+      <c r="J85">
+        <v>2018</v>
       </c>
       <c r="K85">
         <v>2001</v>
@@ -6260,25 +6270,28 @@
       <c r="L85" t="s">
         <v>9</v>
       </c>
+      <c r="M85" t="s">
+        <v>229</v>
+      </c>
       <c r="N85" t="s">
         <v>229</v>
       </c>
     </row>
     <row r="86" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>222</v>
+        <v>60</v>
       </c>
       <c r="B86" t="s">
-        <v>223</v>
+        <v>162</v>
       </c>
       <c r="C86" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="D86" t="s">
         <v>29</v>
       </c>
       <c r="E86" t="s">
-        <v>199</v>
+        <v>11</v>
       </c>
       <c r="F86" t="s">
         <v>17</v>
@@ -6296,10 +6309,10 @@
         <v>9</v>
       </c>
       <c r="K86">
-        <v>2010</v>
+        <v>2001</v>
       </c>
       <c r="L86" t="s">
-        <v>224</v>
+        <v>9</v>
       </c>
       <c r="N86" t="s">
         <v>229</v>
@@ -6307,10 +6320,10 @@
     </row>
     <row r="87" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>62</v>
+        <v>222</v>
       </c>
       <c r="B87" t="s">
-        <v>165</v>
+        <v>223</v>
       </c>
       <c r="C87" t="s">
         <v>191</v>
@@ -6340,116 +6353,116 @@
         <v>2010</v>
       </c>
       <c r="L87" t="s">
-        <v>9</v>
+        <v>224</v>
       </c>
       <c r="N87" t="s">
         <v>229</v>
       </c>
     </row>
     <row r="88" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A88" s="2" t="s">
+      <c r="A88" t="s">
+        <v>62</v>
+      </c>
+      <c r="B88" t="s">
+        <v>165</v>
+      </c>
+      <c r="C88" t="s">
+        <v>191</v>
+      </c>
+      <c r="D88" t="s">
+        <v>29</v>
+      </c>
+      <c r="E88" t="s">
+        <v>199</v>
+      </c>
+      <c r="F88" t="s">
+        <v>17</v>
+      </c>
+      <c r="G88" t="s">
+        <v>8</v>
+      </c>
+      <c r="H88" t="s">
+        <v>31</v>
+      </c>
+      <c r="I88" t="s">
+        <v>9</v>
+      </c>
+      <c r="J88" t="s">
+        <v>9</v>
+      </c>
+      <c r="K88">
+        <v>2010</v>
+      </c>
+      <c r="L88" t="s">
+        <v>9</v>
+      </c>
+      <c r="N88" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="89" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A89" s="2" t="s">
         <v>790</v>
       </c>
-      <c r="B88" s="2" t="s">
+      <c r="B89" s="2" t="s">
         <v>791</v>
       </c>
-      <c r="C88" s="2" t="s">
+      <c r="C89" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D88" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="E88" s="2" t="s">
+      <c r="D89" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E89" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F88" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="G88" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H88" s="2" t="s">
+      <c r="F89" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G89" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H89" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="I88" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="J88" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="K88" s="2">
+      <c r="I89" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="J89" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="K89" s="2">
         <v>2003</v>
       </c>
-      <c r="L88" s="3" t="s">
+      <c r="L89" s="3" t="s">
         <v>224</v>
       </c>
-      <c r="M88" s="2"/>
-      <c r="N88" s="2" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="89" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A89" t="s">
-        <v>48</v>
-      </c>
-      <c r="B89" t="s">
-        <v>148</v>
-      </c>
-      <c r="C89" t="s">
-        <v>188</v>
-      </c>
-      <c r="D89" t="s">
-        <v>29</v>
-      </c>
-      <c r="E89" t="s">
-        <v>11</v>
-      </c>
-      <c r="F89" t="s">
-        <v>17</v>
-      </c>
-      <c r="G89" t="s">
-        <v>8</v>
-      </c>
-      <c r="H89" t="s">
-        <v>31</v>
-      </c>
-      <c r="I89" t="s">
-        <v>9</v>
-      </c>
-      <c r="J89" t="s">
-        <v>9</v>
-      </c>
-      <c r="K89">
-        <v>2001</v>
-      </c>
-      <c r="L89" t="s">
-        <v>9</v>
-      </c>
-      <c r="N89" t="s">
+      <c r="M89" s="2"/>
+      <c r="N89" s="2" t="s">
         <v>229</v>
       </c>
     </row>
     <row r="90" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="B90" t="s">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="C90" t="s">
-        <v>159</v>
+        <v>188</v>
       </c>
       <c r="D90" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="E90" t="s">
         <v>11</v>
       </c>
       <c r="F90" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="G90" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="H90" t="s">
         <v>31</v>
@@ -6472,16 +6485,16 @@
     </row>
     <row r="91" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B91" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="C91" t="s">
-        <v>186</v>
+        <v>159</v>
       </c>
       <c r="D91" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="E91" t="s">
         <v>11</v>
@@ -6513,28 +6526,28 @@
     </row>
     <row r="92" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>210</v>
+        <v>58</v>
       </c>
       <c r="B92" t="s">
-        <v>211</v>
+        <v>160</v>
       </c>
       <c r="C92" t="s">
-        <v>212</v>
+        <v>186</v>
       </c>
       <c r="D92" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="E92" t="s">
-        <v>213</v>
+        <v>11</v>
       </c>
       <c r="F92" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="G92" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="H92" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="I92" t="s">
         <v>9</v>
@@ -6543,10 +6556,10 @@
         <v>9</v>
       </c>
       <c r="K92">
-        <v>2010</v>
+        <v>2001</v>
       </c>
       <c r="L92" t="s">
-        <v>224</v>
+        <v>9</v>
       </c>
       <c r="N92" t="s">
         <v>229</v>
@@ -6554,19 +6567,19 @@
     </row>
     <row r="93" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="B93" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="C93" t="s">
-        <v>191</v>
+        <v>212</v>
       </c>
       <c r="D93" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="E93" t="s">
-        <v>197</v>
+        <v>213</v>
       </c>
       <c r="F93" t="s">
         <v>17</v>
@@ -6595,19 +6608,19 @@
     </row>
     <row r="94" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="B94" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="C94" t="s">
-        <v>218</v>
+        <v>191</v>
       </c>
       <c r="D94" t="s">
         <v>29</v>
       </c>
       <c r="E94" t="s">
-        <v>219</v>
+        <v>197</v>
       </c>
       <c r="F94" t="s">
         <v>17</v>
@@ -6636,19 +6649,19 @@
     </row>
     <row r="95" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>234</v>
+        <v>216</v>
       </c>
       <c r="B95" t="s">
-        <v>245</v>
+        <v>217</v>
       </c>
       <c r="C95" t="s">
-        <v>188</v>
+        <v>218</v>
       </c>
       <c r="D95" t="s">
         <v>29</v>
       </c>
       <c r="E95" t="s">
-        <v>11</v>
+        <v>219</v>
       </c>
       <c r="F95" t="s">
         <v>17</v>
@@ -6657,7 +6670,7 @@
         <v>8</v>
       </c>
       <c r="H95" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="I95" t="s">
         <v>9</v>
@@ -6677,10 +6690,10 @@
     </row>
     <row r="96" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>47</v>
+        <v>234</v>
       </c>
       <c r="B96" t="s">
-        <v>150</v>
+        <v>245</v>
       </c>
       <c r="C96" t="s">
         <v>188</v>
@@ -6707,10 +6720,10 @@
         <v>9</v>
       </c>
       <c r="K96">
-        <v>2001</v>
+        <v>2010</v>
       </c>
       <c r="L96" t="s">
-        <v>9</v>
+        <v>224</v>
       </c>
       <c r="N96" t="s">
         <v>229</v>
@@ -6718,13 +6731,13 @@
     </row>
     <row r="97" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>72</v>
+        <v>47</v>
       </c>
       <c r="B97" t="s">
-        <v>175</v>
+        <v>150</v>
       </c>
       <c r="C97" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="D97" t="s">
         <v>29</v>
@@ -6759,13 +6772,13 @@
     </row>
     <row r="98" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>52</v>
+        <v>72</v>
       </c>
       <c r="B98" t="s">
-        <v>147</v>
+        <v>175</v>
       </c>
       <c r="C98" t="s">
-        <v>187</v>
+        <v>194</v>
       </c>
       <c r="D98" t="s">
         <v>29</v>
@@ -6800,10 +6813,10 @@
     </row>
     <row r="99" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B99" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C99" t="s">
         <v>187</v>
@@ -6841,19 +6854,19 @@
     </row>
     <row r="100" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>220</v>
+        <v>51</v>
       </c>
       <c r="B100" t="s">
-        <v>242</v>
+        <v>146</v>
       </c>
       <c r="C100" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="D100" t="s">
         <v>29</v>
       </c>
       <c r="E100" t="s">
-        <v>197</v>
+        <v>11</v>
       </c>
       <c r="F100" t="s">
         <v>17</v>
@@ -6871,10 +6884,10 @@
         <v>9</v>
       </c>
       <c r="K100">
-        <v>2010</v>
+        <v>2001</v>
       </c>
       <c r="L100" t="s">
-        <v>224</v>
+        <v>9</v>
       </c>
       <c r="N100" t="s">
         <v>229</v>
@@ -6882,10 +6895,10 @@
     </row>
     <row r="101" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>64</v>
+        <v>220</v>
       </c>
       <c r="B101" t="s">
-        <v>221</v>
+        <v>242</v>
       </c>
       <c r="C101" t="s">
         <v>192</v>
@@ -6912,10 +6925,10 @@
         <v>9</v>
       </c>
       <c r="K101">
-        <v>2001</v>
+        <v>2010</v>
       </c>
       <c r="L101" t="s">
-        <v>9</v>
+        <v>224</v>
       </c>
       <c r="N101" t="s">
         <v>229</v>
@@ -6923,13 +6936,13 @@
     </row>
     <row r="102" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B102" t="s">
-        <v>164</v>
+        <v>221</v>
       </c>
       <c r="C102" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="D102" t="s">
         <v>29</v>
@@ -6964,19 +6977,19 @@
     </row>
     <row r="103" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>225</v>
+        <v>63</v>
       </c>
       <c r="B103" t="s">
-        <v>226</v>
+        <v>164</v>
       </c>
       <c r="C103" t="s">
-        <v>35</v>
+        <v>191</v>
       </c>
       <c r="D103" t="s">
         <v>29</v>
       </c>
       <c r="E103" t="s">
-        <v>17</v>
+        <v>197</v>
       </c>
       <c r="F103" t="s">
         <v>17</v>
@@ -7005,19 +7018,19 @@
     </row>
     <row r="104" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>73</v>
+        <v>225</v>
       </c>
       <c r="B104" t="s">
-        <v>176</v>
+        <v>226</v>
       </c>
       <c r="C104" t="s">
-        <v>195</v>
+        <v>35</v>
       </c>
       <c r="D104" t="s">
         <v>29</v>
       </c>
       <c r="E104" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="F104" t="s">
         <v>17</v>
@@ -7046,13 +7059,13 @@
     </row>
     <row r="105" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>181</v>
+        <v>73</v>
       </c>
       <c r="B105" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="C105" t="s">
-        <v>16</v>
+        <v>195</v>
       </c>
       <c r="D105" t="s">
         <v>29</v>
@@ -7061,7 +7074,7 @@
         <v>11</v>
       </c>
       <c r="F105" t="s">
-        <v>183</v>
+        <v>17</v>
       </c>
       <c r="G105" t="s">
         <v>8</v>
@@ -7087,13 +7100,13 @@
     </row>
     <row r="106" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>59</v>
+        <v>181</v>
       </c>
       <c r="B106" t="s">
-        <v>161</v>
+        <v>182</v>
       </c>
       <c r="C106" t="s">
-        <v>188</v>
+        <v>16</v>
       </c>
       <c r="D106" t="s">
         <v>29</v>
@@ -7102,7 +7115,7 @@
         <v>11</v>
       </c>
       <c r="F106" t="s">
-        <v>17</v>
+        <v>183</v>
       </c>
       <c r="G106" t="s">
         <v>8</v>
@@ -7128,10 +7141,10 @@
     </row>
     <row r="107" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="B107" t="s">
-        <v>149</v>
+        <v>161</v>
       </c>
       <c r="C107" t="s">
         <v>188</v>
@@ -7169,10 +7182,10 @@
     </row>
     <row r="108" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="B108" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="C108" t="s">
         <v>188</v>
@@ -7210,10 +7223,10 @@
     </row>
     <row r="109" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B109" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C109" t="s">
         <v>188</v>
@@ -7251,10 +7264,10 @@
     </row>
     <row r="110" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>189</v>
+        <v>54</v>
       </c>
       <c r="B110" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="C110" t="s">
         <v>188</v>
@@ -7292,10 +7305,10 @@
     </row>
     <row r="111" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>86</v>
+        <v>189</v>
       </c>
       <c r="B111" t="s">
-        <v>140</v>
+        <v>154</v>
       </c>
       <c r="C111" t="s">
         <v>188</v>
@@ -7333,10 +7346,10 @@
     </row>
     <row r="112" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B112" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C112" t="s">
         <v>188</v>
@@ -7374,10 +7387,10 @@
     </row>
     <row r="113" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B113" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C113" t="s">
         <v>188</v>
@@ -7415,10 +7428,10 @@
     </row>
     <row r="114" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B114" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C114" t="s">
         <v>188</v>
@@ -7456,10 +7469,10 @@
     </row>
     <row r="115" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B115" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C115" t="s">
         <v>188</v>
@@ -7497,10 +7510,10 @@
     </row>
     <row r="116" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B116" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C116" t="s">
         <v>188</v>
@@ -7538,13 +7551,13 @@
     </row>
     <row r="117" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>740</v>
+        <v>81</v>
       </c>
       <c r="B117" t="s">
-        <v>741</v>
+        <v>135</v>
       </c>
       <c r="C117" t="s">
-        <v>159</v>
+        <v>188</v>
       </c>
       <c r="D117" t="s">
         <v>29</v>
@@ -7561,51 +7574,69 @@
       <c r="H117" t="s">
         <v>31</v>
       </c>
+      <c r="I117" t="s">
+        <v>9</v>
+      </c>
+      <c r="J117" t="s">
+        <v>9</v>
+      </c>
       <c r="K117">
         <v>2001</v>
       </c>
+      <c r="L117" t="s">
+        <v>9</v>
+      </c>
       <c r="N117" t="s">
         <v>229</v>
       </c>
     </row>
     <row r="118" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>279</v>
+        <v>740</v>
       </c>
       <c r="B118" t="s">
-        <v>295</v>
+        <v>741</v>
+      </c>
+      <c r="C118" t="s">
+        <v>159</v>
       </c>
       <c r="D118" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="E118" t="s">
-        <v>311</v>
+        <v>11</v>
       </c>
       <c r="F118" t="s">
-        <v>199</v>
+        <v>17</v>
       </c>
       <c r="G118" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="H118" t="s">
-        <v>313</v>
+        <v>31</v>
+      </c>
+      <c r="K118">
+        <v>2001</v>
+      </c>
+      <c r="N118" t="s">
+        <v>229</v>
       </c>
     </row>
     <row r="119" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B119" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="D119" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="E119" t="s">
+        <v>311</v>
+      </c>
+      <c r="F119" t="s">
         <v>199</v>
-      </c>
-      <c r="F119" t="s">
-        <v>17</v>
       </c>
       <c r="G119" t="s">
         <v>17</v>
@@ -7616,19 +7647,19 @@
     </row>
     <row r="120" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B120" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="D120" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="E120" t="s">
-        <v>311</v>
+        <v>199</v>
       </c>
       <c r="F120" t="s">
-        <v>311</v>
+        <v>17</v>
       </c>
       <c r="G120" t="s">
         <v>17</v>
@@ -7639,10 +7670,10 @@
     </row>
     <row r="121" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B121" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="D121" t="s">
         <v>17</v>
@@ -7662,10 +7693,10 @@
     </row>
     <row r="122" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B122" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="D122" t="s">
         <v>17</v>
@@ -7674,30 +7705,24 @@
         <v>311</v>
       </c>
       <c r="F122" t="s">
-        <v>17</v>
+        <v>311</v>
       </c>
       <c r="G122" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="H122" t="s">
         <v>313</v>
       </c>
-      <c r="J122">
-        <v>2014</v>
-      </c>
-      <c r="K122">
-        <v>2014</v>
-      </c>
     </row>
     <row r="123" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B123" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="D123" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="E123" t="s">
         <v>311</v>
@@ -7711,22 +7736,25 @@
       <c r="H123" t="s">
         <v>313</v>
       </c>
+      <c r="J123">
+        <v>2014</v>
+      </c>
       <c r="K123">
-        <v>2001</v>
+        <v>2014</v>
       </c>
     </row>
     <row r="124" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B124" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="D124" t="s">
         <v>29</v>
       </c>
       <c r="E124" t="s">
-        <v>199</v>
+        <v>311</v>
       </c>
       <c r="F124" t="s">
         <v>17</v>
@@ -7743,16 +7771,16 @@
     </row>
     <row r="125" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B125" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="D125" t="s">
         <v>29</v>
       </c>
       <c r="E125" t="s">
-        <v>311</v>
+        <v>199</v>
       </c>
       <c r="F125" t="s">
         <v>17</v>
@@ -7763,25 +7791,22 @@
       <c r="H125" t="s">
         <v>313</v>
       </c>
-      <c r="J125">
-        <v>2014</v>
-      </c>
       <c r="K125">
-        <v>1990</v>
+        <v>2001</v>
       </c>
     </row>
     <row r="126" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B126" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="D126" t="s">
         <v>29</v>
       </c>
       <c r="E126" t="s">
-        <v>17</v>
+        <v>311</v>
       </c>
       <c r="F126" t="s">
         <v>17</v>
@@ -7792,22 +7817,25 @@
       <c r="H126" t="s">
         <v>313</v>
       </c>
+      <c r="J126">
+        <v>2014</v>
+      </c>
       <c r="K126">
-        <v>2001</v>
+        <v>1990</v>
       </c>
     </row>
     <row r="127" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B127" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D127" t="s">
         <v>29</v>
       </c>
       <c r="E127" t="s">
-        <v>311</v>
+        <v>17</v>
       </c>
       <c r="F127" t="s">
         <v>17</v>
@@ -7824,10 +7852,10 @@
     </row>
     <row r="128" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B128" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="D128" t="s">
         <v>29</v>
@@ -7850,10 +7878,10 @@
     </row>
     <row r="129" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B129" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="D129" t="s">
         <v>29</v>
@@ -7876,10 +7904,10 @@
     </row>
     <row r="130" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B130" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="D130" t="s">
         <v>29</v>
@@ -7902,10 +7930,10 @@
     </row>
     <row r="131" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B131" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="D131" t="s">
         <v>29</v>
@@ -7928,10 +7956,10 @@
     </row>
     <row r="132" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B132" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="D132" t="s">
         <v>29</v>
@@ -7954,10 +7982,10 @@
     </row>
     <row r="133" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B133" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="D133" t="s">
         <v>29</v>
@@ -7966,24 +7994,24 @@
         <v>311</v>
       </c>
       <c r="F133" t="s">
-        <v>312</v>
+        <v>17</v>
       </c>
       <c r="G133" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="H133" t="s">
         <v>313</v>
       </c>
       <c r="K133">
-        <v>2014</v>
+        <v>2001</v>
       </c>
     </row>
     <row r="134" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>349</v>
+        <v>294</v>
       </c>
       <c r="B134" t="s">
-        <v>362</v>
+        <v>310</v>
       </c>
       <c r="D134" t="s">
         <v>29</v>
@@ -7992,10 +8020,10 @@
         <v>311</v>
       </c>
       <c r="F134" t="s">
-        <v>17</v>
+        <v>312</v>
       </c>
       <c r="G134" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="H134" t="s">
         <v>313</v>
@@ -8006,10 +8034,10 @@
     </row>
     <row r="135" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B135" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="D135" t="s">
         <v>29</v>
@@ -8032,19 +8060,16 @@
     </row>
     <row r="136" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B136" t="s">
-        <v>364</v>
-      </c>
-      <c r="C136" t="s">
-        <v>35</v>
+        <v>363</v>
       </c>
       <c r="D136" t="s">
         <v>29</v>
       </c>
       <c r="E136" t="s">
-        <v>199</v>
+        <v>311</v>
       </c>
       <c r="F136" t="s">
         <v>17</v>
@@ -8061,16 +8086,19 @@
     </row>
     <row r="137" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B137" t="s">
-        <v>365</v>
+        <v>364</v>
+      </c>
+      <c r="C137" t="s">
+        <v>35</v>
       </c>
       <c r="D137" t="s">
         <v>29</v>
       </c>
       <c r="E137" t="s">
-        <v>311</v>
+        <v>199</v>
       </c>
       <c r="F137" t="s">
         <v>17</v>
@@ -8082,15 +8110,15 @@
         <v>313</v>
       </c>
       <c r="K137">
-        <v>2010</v>
+        <v>2014</v>
       </c>
     </row>
     <row r="138" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B138" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="D138" t="s">
         <v>29</v>
@@ -8107,13 +8135,16 @@
       <c r="H138" t="s">
         <v>313</v>
       </c>
+      <c r="K138">
+        <v>2010</v>
+      </c>
     </row>
     <row r="139" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>377</v>
+        <v>353</v>
       </c>
       <c r="B139" t="s">
-        <v>378</v>
+        <v>366</v>
       </c>
       <c r="D139" t="s">
         <v>29</v>
@@ -8130,16 +8161,13 @@
       <c r="H139" t="s">
         <v>313</v>
       </c>
-      <c r="K139">
-        <v>2014</v>
-      </c>
     </row>
     <row r="140" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>354</v>
+        <v>377</v>
       </c>
       <c r="B140" t="s">
-        <v>367</v>
+        <v>378</v>
       </c>
       <c r="D140" t="s">
         <v>29</v>
@@ -8162,7 +8190,7 @@
     </row>
     <row r="141" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B141" t="s">
         <v>367</v>
@@ -8188,7 +8216,7 @@
     </row>
     <row r="142" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B142" t="s">
         <v>367</v>
@@ -8214,10 +8242,10 @@
     </row>
     <row r="143" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B143" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="D143" t="s">
         <v>29</v>
@@ -8240,10 +8268,10 @@
     </row>
     <row r="144" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B144" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="D144" t="s">
         <v>29</v>
@@ -8266,10 +8294,10 @@
     </row>
     <row r="145" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>370</v>
+        <v>358</v>
       </c>
       <c r="B145" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="D145" t="s">
         <v>29</v>
@@ -8292,10 +8320,10 @@
     </row>
     <row r="146" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>359</v>
+        <v>370</v>
       </c>
       <c r="B146" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="D146" t="s">
         <v>29</v>
@@ -8318,10 +8346,10 @@
     </row>
     <row r="147" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B147" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="D147" t="s">
         <v>29</v>
@@ -8344,10 +8372,10 @@
     </row>
     <row r="148" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>476</v>
+        <v>360</v>
       </c>
       <c r="B148" t="s">
-        <v>477</v>
+        <v>373</v>
       </c>
       <c r="D148" t="s">
         <v>29</v>
@@ -8370,10 +8398,10 @@
     </row>
     <row r="149" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>375</v>
+        <v>476</v>
       </c>
       <c r="B149" t="s">
-        <v>376</v>
+        <v>477</v>
       </c>
       <c r="D149" t="s">
         <v>29</v>
@@ -8390,25 +8418,22 @@
       <c r="H149" t="s">
         <v>313</v>
       </c>
-      <c r="J149">
-        <v>2014</v>
-      </c>
       <c r="K149">
         <v>2014</v>
       </c>
     </row>
     <row r="150" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>361</v>
+        <v>375</v>
       </c>
       <c r="B150" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="D150" t="s">
         <v>29</v>
       </c>
       <c r="E150" t="s">
-        <v>199</v>
+        <v>311</v>
       </c>
       <c r="F150" t="s">
         <v>17</v>
@@ -8419,22 +8444,25 @@
       <c r="H150" t="s">
         <v>313</v>
       </c>
+      <c r="J150">
+        <v>2014</v>
+      </c>
       <c r="K150">
         <v>2014</v>
       </c>
     </row>
     <row r="151" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>326</v>
+        <v>361</v>
       </c>
       <c r="B151" t="s">
-        <v>340</v>
+        <v>374</v>
       </c>
       <c r="D151" t="s">
         <v>29</v>
       </c>
       <c r="E151" t="s">
-        <v>343</v>
+        <v>199</v>
       </c>
       <c r="F151" t="s">
         <v>17</v>
@@ -8443,18 +8471,18 @@
         <v>8</v>
       </c>
       <c r="H151" t="s">
-        <v>384</v>
+        <v>313</v>
       </c>
       <c r="K151">
-        <v>2001</v>
+        <v>2014</v>
       </c>
     </row>
     <row r="152" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>473</v>
+        <v>326</v>
       </c>
       <c r="B152" t="s">
-        <v>382</v>
+        <v>340</v>
       </c>
       <c r="D152" t="s">
         <v>29</v>
@@ -8472,12 +8500,12 @@
         <v>384</v>
       </c>
       <c r="K152">
-        <v>2017</v>
+        <v>2001</v>
       </c>
     </row>
     <row r="153" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>397</v>
+        <v>473</v>
       </c>
       <c r="B153" t="s">
         <v>382</v>
@@ -8503,10 +8531,10 @@
     </row>
     <row r="154" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>314</v>
+        <v>397</v>
       </c>
       <c r="B154" t="s">
-        <v>329</v>
+        <v>382</v>
       </c>
       <c r="D154" t="s">
         <v>29</v>
@@ -8524,15 +8552,15 @@
         <v>384</v>
       </c>
       <c r="K154">
-        <v>2001</v>
+        <v>2017</v>
       </c>
     </row>
     <row r="155" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="B155" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="D155" t="s">
         <v>29</v>
@@ -8555,10 +8583,10 @@
     </row>
     <row r="156" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>325</v>
+        <v>318</v>
       </c>
       <c r="B156" t="s">
-        <v>339</v>
+        <v>332</v>
       </c>
       <c r="D156" t="s">
         <v>29</v>
@@ -8581,10 +8609,10 @@
     </row>
     <row r="157" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>392</v>
+        <v>325</v>
       </c>
       <c r="B157" t="s">
-        <v>796</v>
+        <v>339</v>
       </c>
       <c r="D157" t="s">
         <v>29</v>
@@ -8602,73 +8630,73 @@
         <v>384</v>
       </c>
       <c r="K157">
-        <v>2017</v>
+        <v>2001</v>
       </c>
     </row>
     <row r="158" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>323</v>
+        <v>392</v>
       </c>
       <c r="B158" t="s">
-        <v>337</v>
+        <v>796</v>
       </c>
       <c r="D158" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="E158" t="s">
         <v>343</v>
       </c>
       <c r="F158" t="s">
-        <v>199</v>
+        <v>17</v>
       </c>
       <c r="G158" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="H158" t="s">
         <v>384</v>
       </c>
+      <c r="K158">
+        <v>2017</v>
+      </c>
     </row>
     <row r="159" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>396</v>
+        <v>323</v>
       </c>
       <c r="B159" t="s">
-        <v>797</v>
-      </c>
-      <c r="C159" t="s">
-        <v>795</v>
+        <v>337</v>
       </c>
       <c r="D159" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="E159" t="s">
+        <v>343</v>
+      </c>
+      <c r="F159" t="s">
         <v>199</v>
       </c>
-      <c r="F159" t="s">
-        <v>17</v>
-      </c>
       <c r="G159" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="H159" t="s">
         <v>384</v>
       </c>
-      <c r="K159">
-        <v>2017</v>
-      </c>
     </row>
     <row r="160" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>474</v>
+        <v>396</v>
       </c>
       <c r="B160" t="s">
-        <v>475</v>
+        <v>797</v>
+      </c>
+      <c r="C160" t="s">
+        <v>795</v>
       </c>
       <c r="D160" t="s">
         <v>29</v>
       </c>
       <c r="E160" t="s">
-        <v>343</v>
+        <v>199</v>
       </c>
       <c r="F160" t="s">
         <v>17</v>
@@ -8680,21 +8708,18 @@
         <v>384</v>
       </c>
       <c r="K160">
-        <v>2014</v>
+        <v>2017</v>
       </c>
     </row>
     <row r="161" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>399</v>
+        <v>474</v>
       </c>
       <c r="B161" t="s">
-        <v>798</v>
-      </c>
-      <c r="C161" t="s">
-        <v>799</v>
+        <v>475</v>
       </c>
       <c r="D161" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="E161" t="s">
         <v>343</v>
@@ -8709,18 +8734,21 @@
         <v>384</v>
       </c>
       <c r="K161">
-        <v>2012</v>
+        <v>2014</v>
       </c>
     </row>
     <row r="162" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>319</v>
+        <v>399</v>
       </c>
       <c r="B162" t="s">
-        <v>333</v>
+        <v>798</v>
+      </c>
+      <c r="C162" t="s">
+        <v>799</v>
       </c>
       <c r="D162" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="E162" t="s">
         <v>343</v>
@@ -8734,22 +8762,16 @@
       <c r="H162" t="s">
         <v>384</v>
       </c>
-      <c r="J162">
-        <v>2017</v>
-      </c>
       <c r="K162">
-        <v>1990</v>
+        <v>2012</v>
       </c>
     </row>
     <row r="163" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>383</v>
+        <v>319</v>
       </c>
       <c r="B163" t="s">
-        <v>800</v>
-      </c>
-      <c r="C163" t="s">
-        <v>799</v>
+        <v>333</v>
       </c>
       <c r="D163" t="s">
         <v>29</v>
@@ -8766,16 +8788,22 @@
       <c r="H163" t="s">
         <v>384</v>
       </c>
+      <c r="J163">
+        <v>2017</v>
+      </c>
       <c r="K163">
-        <v>2017</v>
+        <v>1990</v>
       </c>
     </row>
     <row r="164" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>394</v>
+        <v>383</v>
       </c>
       <c r="B164" t="s">
-        <v>801</v>
+        <v>800</v>
+      </c>
+      <c r="C164" t="s">
+        <v>799</v>
       </c>
       <c r="D164" t="s">
         <v>29</v>
@@ -8798,10 +8826,10 @@
     </row>
     <row r="165" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>385</v>
+        <v>394</v>
       </c>
       <c r="B165" t="s">
-        <v>382</v>
+        <v>801</v>
       </c>
       <c r="D165" t="s">
         <v>29</v>
@@ -8824,13 +8852,10 @@
     </row>
     <row r="166" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>398</v>
+        <v>385</v>
       </c>
       <c r="B166" t="s">
-        <v>802</v>
-      </c>
-      <c r="C166" t="s">
-        <v>803</v>
+        <v>382</v>
       </c>
       <c r="D166" t="s">
         <v>29</v>
@@ -8853,13 +8878,13 @@
     </row>
     <row r="167" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>387</v>
+        <v>398</v>
       </c>
       <c r="B167" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="C167" t="s">
-        <v>805</v>
+        <v>803</v>
       </c>
       <c r="D167" t="s">
         <v>29</v>
@@ -8882,33 +8907,39 @@
     </row>
     <row r="168" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>327</v>
+        <v>387</v>
       </c>
       <c r="B168" t="s">
-        <v>341</v>
+        <v>804</v>
+      </c>
+      <c r="C168" t="s">
+        <v>805</v>
       </c>
       <c r="D168" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="E168" t="s">
         <v>343</v>
       </c>
       <c r="F168" t="s">
-        <v>343</v>
+        <v>17</v>
       </c>
       <c r="G168" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="H168" t="s">
         <v>384</v>
       </c>
+      <c r="K168">
+        <v>2017</v>
+      </c>
     </row>
     <row r="169" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>707</v>
+        <v>327</v>
       </c>
       <c r="B169" t="s">
-        <v>708</v>
+        <v>341</v>
       </c>
       <c r="D169" t="s">
         <v>17</v>
@@ -8928,126 +8959,126 @@
     </row>
     <row r="170" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
-        <v>347</v>
+        <v>707</v>
       </c>
       <c r="B170" t="s">
-        <v>348</v>
-      </c>
-      <c r="C170" t="s">
-        <v>25</v>
+        <v>708</v>
       </c>
       <c r="D170" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="E170" t="s">
-        <v>41</v>
+        <v>343</v>
       </c>
       <c r="F170" t="s">
-        <v>17</v>
+        <v>343</v>
       </c>
       <c r="G170" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="H170" t="s">
-        <v>36</v>
-      </c>
-      <c r="I170" t="s">
-        <v>9</v>
-      </c>
-      <c r="J170">
-        <v>2016</v>
-      </c>
-      <c r="K170">
-        <v>2010</v>
-      </c>
-      <c r="L170" t="s">
-        <v>224</v>
-      </c>
-      <c r="N170" t="s">
-        <v>229</v>
+        <v>384</v>
       </c>
     </row>
     <row r="171" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>322</v>
+        <v>347</v>
       </c>
       <c r="B171" t="s">
-        <v>336</v>
+        <v>348</v>
+      </c>
+      <c r="C171" t="s">
+        <v>25</v>
       </c>
       <c r="D171" t="s">
         <v>29</v>
       </c>
       <c r="E171" t="s">
-        <v>344</v>
+        <v>41</v>
       </c>
       <c r="F171" t="s">
         <v>17</v>
       </c>
       <c r="G171" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="H171" t="s">
-        <v>384</v>
+        <v>36</v>
+      </c>
+      <c r="I171" t="s">
+        <v>9</v>
+      </c>
+      <c r="J171">
+        <v>2016</v>
+      </c>
+      <c r="K171">
+        <v>2010</v>
+      </c>
+      <c r="L171" t="s">
+        <v>224</v>
+      </c>
+      <c r="N171" t="s">
+        <v>229</v>
       </c>
     </row>
     <row r="172" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>388</v>
+        <v>322</v>
       </c>
       <c r="B172" t="s">
-        <v>806</v>
-      </c>
-      <c r="C172" t="s">
-        <v>805</v>
+        <v>336</v>
       </c>
       <c r="D172" t="s">
         <v>29</v>
       </c>
       <c r="E172" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="F172" t="s">
         <v>17</v>
       </c>
       <c r="G172" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="H172" t="s">
         <v>384</v>
       </c>
-      <c r="K172">
-        <v>2017</v>
-      </c>
     </row>
     <row r="173" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>710</v>
+        <v>388</v>
       </c>
       <c r="B173" t="s">
-        <v>709</v>
+        <v>806</v>
+      </c>
+      <c r="C173" t="s">
+        <v>805</v>
       </c>
       <c r="D173" t="s">
         <v>29</v>
       </c>
       <c r="E173" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="F173" t="s">
         <v>17</v>
       </c>
       <c r="G173" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="H173" t="s">
         <v>384</v>
       </c>
+      <c r="K173">
+        <v>2017</v>
+      </c>
     </row>
     <row r="174" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
-        <v>345</v>
+        <v>710</v>
       </c>
       <c r="B174" t="s">
-        <v>346</v>
+        <v>709</v>
       </c>
       <c r="D174" t="s">
         <v>29</v>
@@ -9067,33 +9098,30 @@
     </row>
     <row r="175" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
-        <v>390</v>
+        <v>345</v>
       </c>
       <c r="B175" t="s">
-        <v>382</v>
+        <v>346</v>
       </c>
       <c r="D175" t="s">
         <v>29</v>
       </c>
       <c r="E175" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="F175" t="s">
         <v>17</v>
       </c>
       <c r="G175" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="H175" t="s">
         <v>384</v>
       </c>
-      <c r="K175">
-        <v>2017</v>
-      </c>
     </row>
     <row r="176" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B176" t="s">
         <v>382</v>
@@ -9119,7 +9147,7 @@
     </row>
     <row r="177" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
-        <v>395</v>
+        <v>389</v>
       </c>
       <c r="B177" t="s">
         <v>382</v>
@@ -9145,7 +9173,7 @@
     </row>
     <row r="178" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="B178" t="s">
         <v>382</v>
@@ -9171,19 +9199,16 @@
     </row>
     <row r="179" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
-        <v>379</v>
+        <v>391</v>
       </c>
       <c r="B179" t="s">
-        <v>380</v>
-      </c>
-      <c r="C179" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="D179" t="s">
         <v>29</v>
       </c>
       <c r="E179" t="s">
-        <v>199</v>
+        <v>343</v>
       </c>
       <c r="F179" t="s">
         <v>17</v>
@@ -9194,25 +9219,25 @@
       <c r="H179" t="s">
         <v>384</v>
       </c>
-      <c r="J179">
-        <v>2016</v>
-      </c>
       <c r="K179">
-        <v>2010</v>
+        <v>2017</v>
       </c>
     </row>
     <row r="180" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
-        <v>321</v>
+        <v>379</v>
       </c>
       <c r="B180" t="s">
-        <v>335</v>
+        <v>380</v>
+      </c>
+      <c r="C180" t="s">
+        <v>381</v>
       </c>
       <c r="D180" t="s">
         <v>29</v>
       </c>
       <c r="E180" t="s">
-        <v>17</v>
+        <v>199</v>
       </c>
       <c r="F180" t="s">
         <v>17</v>
@@ -9223,22 +9248,25 @@
       <c r="H180" t="s">
         <v>384</v>
       </c>
+      <c r="J180">
+        <v>2016</v>
+      </c>
       <c r="K180">
-        <v>2001</v>
+        <v>2010</v>
       </c>
     </row>
     <row r="181" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="B181" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="D181" t="s">
         <v>29</v>
       </c>
       <c r="E181" t="s">
-        <v>343</v>
+        <v>17</v>
       </c>
       <c r="F181" t="s">
         <v>17</v>
@@ -9255,16 +9283,16 @@
     </row>
     <row r="182" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="B182" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="D182" t="s">
         <v>29</v>
       </c>
       <c r="E182" t="s">
-        <v>17</v>
+        <v>343</v>
       </c>
       <c r="F182" t="s">
         <v>17</v>
@@ -9281,19 +9309,19 @@
     </row>
     <row r="183" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
-        <v>386</v>
+        <v>315</v>
       </c>
       <c r="B183" t="s">
-        <v>382</v>
+        <v>330</v>
       </c>
       <c r="D183" t="s">
         <v>29</v>
       </c>
       <c r="E183" t="s">
-        <v>343</v>
+        <v>17</v>
       </c>
       <c r="F183" t="s">
-        <v>344</v>
+        <v>17</v>
       </c>
       <c r="G183" t="s">
         <v>8</v>
@@ -9302,24 +9330,24 @@
         <v>384</v>
       </c>
       <c r="K183">
-        <v>2017</v>
+        <v>2001</v>
       </c>
     </row>
     <row r="184" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
-        <v>711</v>
+        <v>386</v>
       </c>
       <c r="B184" t="s">
-        <v>712</v>
+        <v>382</v>
       </c>
       <c r="D184" t="s">
         <v>29</v>
       </c>
       <c r="E184" t="s">
-        <v>17</v>
+        <v>343</v>
       </c>
       <c r="F184" t="s">
-        <v>17</v>
+        <v>344</v>
       </c>
       <c r="G184" t="s">
         <v>8</v>
@@ -9328,15 +9356,15 @@
         <v>384</v>
       </c>
       <c r="K184">
-        <v>2001</v>
+        <v>2017</v>
       </c>
     </row>
     <row r="185" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
-        <v>320</v>
+        <v>711</v>
       </c>
       <c r="B185" t="s">
-        <v>334</v>
+        <v>712</v>
       </c>
       <c r="D185" t="s">
         <v>29</v>
@@ -9359,16 +9387,16 @@
     </row>
     <row r="186" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
-        <v>393</v>
+        <v>320</v>
       </c>
       <c r="B186" t="s">
-        <v>382</v>
+        <v>334</v>
       </c>
       <c r="D186" t="s">
         <v>29</v>
       </c>
       <c r="E186" t="s">
-        <v>343</v>
+        <v>17</v>
       </c>
       <c r="F186" t="s">
         <v>17</v>
@@ -9380,21 +9408,21 @@
         <v>384</v>
       </c>
       <c r="K186">
-        <v>2017</v>
+        <v>2001</v>
       </c>
     </row>
     <row r="187" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
-        <v>324</v>
+        <v>393</v>
       </c>
       <c r="B187" t="s">
-        <v>338</v>
+        <v>382</v>
       </c>
       <c r="D187" t="s">
         <v>29</v>
       </c>
       <c r="E187" t="s">
-        <v>17</v>
+        <v>343</v>
       </c>
       <c r="F187" t="s">
         <v>17</v>
@@ -9406,85 +9434,70 @@
         <v>384</v>
       </c>
       <c r="K187">
-        <v>2001</v>
+        <v>2017</v>
       </c>
     </row>
     <row r="188" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
-        <v>316</v>
+        <v>324</v>
       </c>
       <c r="B188" t="s">
-        <v>328</v>
+        <v>338</v>
       </c>
       <c r="D188" t="s">
         <v>29</v>
       </c>
       <c r="E188" t="s">
-        <v>343</v>
+        <v>17</v>
       </c>
       <c r="F188" t="s">
-        <v>342</v>
+        <v>17</v>
       </c>
       <c r="G188" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="H188" t="s">
         <v>384</v>
       </c>
       <c r="K188">
-        <v>2014</v>
+        <v>2001</v>
       </c>
     </row>
     <row r="189" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
-        <v>494</v>
+        <v>316</v>
       </c>
       <c r="B189" t="s">
-        <v>610</v>
-      </c>
-      <c r="C189" t="s">
-        <v>35</v>
+        <v>328</v>
       </c>
       <c r="D189" t="s">
         <v>29</v>
       </c>
       <c r="E189" t="s">
-        <v>275</v>
+        <v>343</v>
       </c>
       <c r="F189" t="s">
-        <v>17</v>
+        <v>342</v>
       </c>
       <c r="G189" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="H189" t="s">
-        <v>277</v>
-      </c>
-      <c r="I189">
-        <v>1970</v>
-      </c>
-      <c r="J189">
-        <v>2015</v>
+        <v>384</v>
       </c>
       <c r="K189">
-        <v>1970</v>
-      </c>
-      <c r="M189" t="s">
-        <v>229</v>
-      </c>
-      <c r="N189" t="s">
-        <v>229</v>
+        <v>2014</v>
       </c>
     </row>
     <row r="190" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="B190" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="C190" t="s">
-        <v>159</v>
+        <v>35</v>
       </c>
       <c r="D190" t="s">
         <v>29</v>
@@ -9501,17 +9514,14 @@
       <c r="H190" t="s">
         <v>277</v>
       </c>
-      <c r="I190" t="s">
-        <v>9</v>
-      </c>
-      <c r="J190" t="s">
-        <v>9</v>
+      <c r="I190">
+        <v>1970</v>
+      </c>
+      <c r="J190">
+        <v>2015</v>
       </c>
       <c r="K190">
-        <v>2015</v>
-      </c>
-      <c r="L190" t="s">
-        <v>9</v>
+        <v>1970</v>
       </c>
       <c r="M190" t="s">
         <v>229</v>
@@ -9522,16 +9532,16 @@
     </row>
     <row r="191" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="B191" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="C191" t="s">
-        <v>16</v>
+        <v>159</v>
       </c>
       <c r="D191" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="E191" t="s">
         <v>275</v>
@@ -9554,6 +9564,9 @@
       <c r="K191">
         <v>2015</v>
       </c>
+      <c r="L191" t="s">
+        <v>9</v>
+      </c>
       <c r="M191" t="s">
         <v>229</v>
       </c>
@@ -9563,16 +9576,16 @@
     </row>
     <row r="192" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="B192" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="C192" t="s">
         <v>16</v>
       </c>
       <c r="D192" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="E192" t="s">
         <v>275</v>
@@ -9586,14 +9599,14 @@
       <c r="H192" t="s">
         <v>277</v>
       </c>
-      <c r="I192">
-        <v>1971</v>
-      </c>
-      <c r="J192">
+      <c r="I192" t="s">
+        <v>9</v>
+      </c>
+      <c r="J192" t="s">
+        <v>9</v>
+      </c>
+      <c r="K192">
         <v>2015</v>
-      </c>
-      <c r="K192">
-        <v>1971</v>
       </c>
       <c r="M192" t="s">
         <v>229</v>
@@ -9604,10 +9617,10 @@
     </row>
     <row r="193" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="B193" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="C193" t="s">
         <v>16</v>
@@ -9628,13 +9641,13 @@
         <v>277</v>
       </c>
       <c r="I193">
-        <v>1970</v>
+        <v>1971</v>
       </c>
       <c r="J193">
         <v>2015</v>
       </c>
       <c r="K193">
-        <v>1970</v>
+        <v>1971</v>
       </c>
       <c r="M193" t="s">
         <v>229</v>
@@ -9645,34 +9658,37 @@
     </row>
     <row r="194" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="B194" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="C194" t="s">
-        <v>186</v>
+        <v>16</v>
       </c>
       <c r="D194" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="E194" t="s">
         <v>275</v>
       </c>
       <c r="F194" t="s">
-        <v>275</v>
+        <v>17</v>
       </c>
       <c r="G194" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="H194" t="s">
         <v>277</v>
       </c>
-      <c r="I194" t="s">
-        <v>9</v>
-      </c>
-      <c r="J194" t="s">
-        <v>9</v>
+      <c r="I194">
+        <v>1970</v>
+      </c>
+      <c r="J194">
+        <v>2015</v>
+      </c>
+      <c r="K194">
+        <v>1970</v>
       </c>
       <c r="M194" t="s">
         <v>229</v>
@@ -9683,22 +9699,22 @@
     </row>
     <row r="195" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
-        <v>590</v>
+        <v>499</v>
       </c>
       <c r="B195" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="C195" t="s">
-        <v>259</v>
+        <v>186</v>
       </c>
       <c r="D195" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="E195" t="s">
         <v>275</v>
       </c>
       <c r="F195" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="G195" t="s">
         <v>17</v>
@@ -9721,13 +9737,13 @@
     </row>
     <row r="196" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
-        <v>500</v>
+        <v>590</v>
       </c>
       <c r="B196" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="C196" t="s">
-        <v>159</v>
+        <v>259</v>
       </c>
       <c r="D196" t="s">
         <v>29</v>
@@ -9736,22 +9752,19 @@
         <v>275</v>
       </c>
       <c r="F196" t="s">
-        <v>17</v>
+        <v>276</v>
       </c>
       <c r="G196" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="H196" t="s">
         <v>277</v>
       </c>
-      <c r="I196">
-        <v>2000</v>
-      </c>
-      <c r="J196">
-        <v>2015</v>
-      </c>
-      <c r="K196">
-        <v>2000</v>
+      <c r="I196" t="s">
+        <v>9</v>
+      </c>
+      <c r="J196" t="s">
+        <v>9</v>
       </c>
       <c r="M196" t="s">
         <v>229</v>
@@ -9762,34 +9775,37 @@
     </row>
     <row r="197" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="B197" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="C197" t="s">
         <v>159</v>
       </c>
       <c r="D197" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="E197" t="s">
         <v>275</v>
       </c>
       <c r="F197" t="s">
-        <v>275</v>
+        <v>17</v>
       </c>
       <c r="G197" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="H197" t="s">
         <v>277</v>
       </c>
-      <c r="I197" t="s">
-        <v>9</v>
-      </c>
-      <c r="J197" t="s">
-        <v>9</v>
+      <c r="I197">
+        <v>2000</v>
+      </c>
+      <c r="J197">
+        <v>2015</v>
+      </c>
+      <c r="K197">
+        <v>2000</v>
       </c>
       <c r="M197" t="s">
         <v>229</v>
@@ -9800,25 +9816,25 @@
     </row>
     <row r="198" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="B198" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="C198" t="s">
-        <v>35</v>
+        <v>159</v>
       </c>
       <c r="D198" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="E198" t="s">
         <v>275</v>
       </c>
       <c r="F198" t="s">
-        <v>17</v>
+        <v>275</v>
       </c>
       <c r="G198" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="H198" t="s">
         <v>277</v>
@@ -9829,9 +9845,6 @@
       <c r="J198" t="s">
         <v>9</v>
       </c>
-      <c r="K198">
-        <v>2000</v>
-      </c>
       <c r="M198" t="s">
         <v>229</v>
       </c>
@@ -9841,13 +9854,13 @@
     </row>
     <row r="199" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="B199" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="C199" t="s">
-        <v>278</v>
+        <v>35</v>
       </c>
       <c r="D199" t="s">
         <v>29</v>
@@ -9882,10 +9895,10 @@
     </row>
     <row r="200" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="B200" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="C200" t="s">
         <v>278</v>
@@ -9923,10 +9936,10 @@
     </row>
     <row r="201" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="B201" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="C201" t="s">
         <v>278</v>
@@ -9964,13 +9977,13 @@
     </row>
     <row r="202" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
-        <v>565</v>
+        <v>505</v>
       </c>
       <c r="B202" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="C202" t="s">
-        <v>564</v>
+        <v>278</v>
       </c>
       <c r="D202" t="s">
         <v>29</v>
@@ -9987,22 +10000,34 @@
       <c r="H202" t="s">
         <v>277</v>
       </c>
+      <c r="I202" t="s">
+        <v>9</v>
+      </c>
+      <c r="J202" t="s">
+        <v>9</v>
+      </c>
       <c r="K202">
         <v>2000</v>
       </c>
+      <c r="M202" t="s">
+        <v>229</v>
+      </c>
+      <c r="N202" t="s">
+        <v>229</v>
+      </c>
     </row>
     <row r="203" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="B203" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="C203" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="D203" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="E203" t="s">
         <v>275</v>
@@ -10022,13 +10047,16 @@
     </row>
     <row r="204" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
-        <v>506</v>
+        <v>566</v>
       </c>
       <c r="B204" t="s">
-        <v>625</v>
+        <v>624</v>
+      </c>
+      <c r="C204" t="s">
+        <v>563</v>
       </c>
       <c r="D204" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="E204" t="s">
         <v>275</v>
@@ -10045,22 +10073,13 @@
       <c r="K204">
         <v>2000</v>
       </c>
-      <c r="M204" t="s">
-        <v>229</v>
-      </c>
-      <c r="N204" t="s">
-        <v>229</v>
-      </c>
     </row>
     <row r="205" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
-        <v>578</v>
+        <v>506</v>
       </c>
       <c r="B205" t="s">
-        <v>626</v>
-      </c>
-      <c r="C205" t="s">
-        <v>16</v>
+        <v>625</v>
       </c>
       <c r="D205" t="s">
         <v>29</v>
@@ -10080,16 +10099,22 @@
       <c r="K205">
         <v>2000</v>
       </c>
+      <c r="M205" t="s">
+        <v>229</v>
+      </c>
+      <c r="N205" t="s">
+        <v>229</v>
+      </c>
     </row>
     <row r="206" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="B206" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="C206" t="s">
-        <v>159</v>
+        <v>16</v>
       </c>
       <c r="D206" t="s">
         <v>29</v>
@@ -10112,10 +10137,10 @@
     </row>
     <row r="207" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="B207" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="C207" t="s">
         <v>159</v>
@@ -10141,13 +10166,13 @@
     </row>
     <row r="208" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
-        <v>507</v>
+        <v>580</v>
       </c>
       <c r="B208" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="C208" t="s">
-        <v>35</v>
+        <v>159</v>
       </c>
       <c r="D208" t="s">
         <v>29</v>
@@ -10162,33 +10187,21 @@
         <v>8</v>
       </c>
       <c r="H208" t="s">
-        <v>520</v>
-      </c>
-      <c r="I208">
-        <v>1970</v>
-      </c>
-      <c r="J208">
-        <v>2015</v>
+        <v>277</v>
       </c>
       <c r="K208">
-        <v>1970</v>
-      </c>
-      <c r="M208" t="s">
-        <v>229</v>
-      </c>
-      <c r="N208" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="209" spans="1:14" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="209" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B209" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="C209" t="s">
-        <v>159</v>
+        <v>35</v>
       </c>
       <c r="D209" t="s">
         <v>29</v>
@@ -10205,17 +10218,14 @@
       <c r="H209" t="s">
         <v>520</v>
       </c>
-      <c r="I209" t="s">
-        <v>9</v>
-      </c>
-      <c r="J209" t="s">
-        <v>9</v>
+      <c r="I209">
+        <v>1970</v>
+      </c>
+      <c r="J209">
+        <v>2015</v>
       </c>
       <c r="K209">
-        <v>2015</v>
-      </c>
-      <c r="L209" t="s">
-        <v>9</v>
+        <v>1970</v>
       </c>
       <c r="M209" t="s">
         <v>229</v>
@@ -10224,18 +10234,18 @@
         <v>229</v>
       </c>
     </row>
-    <row r="210" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:14" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="B210" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="C210" t="s">
-        <v>16</v>
+        <v>159</v>
       </c>
       <c r="D210" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="E210" t="s">
         <v>275</v>
@@ -10258,6 +10268,9 @@
       <c r="K210">
         <v>2015</v>
       </c>
+      <c r="L210" t="s">
+        <v>9</v>
+      </c>
       <c r="M210" t="s">
         <v>229</v>
       </c>
@@ -10267,16 +10280,16 @@
     </row>
     <row r="211" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="B211" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="C211" t="s">
         <v>16</v>
       </c>
       <c r="D211" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="E211" t="s">
         <v>275</v>
@@ -10290,14 +10303,14 @@
       <c r="H211" t="s">
         <v>520</v>
       </c>
-      <c r="I211">
-        <v>1971</v>
-      </c>
-      <c r="J211">
+      <c r="I211" t="s">
+        <v>9</v>
+      </c>
+      <c r="J211" t="s">
+        <v>9</v>
+      </c>
+      <c r="K211">
         <v>2015</v>
-      </c>
-      <c r="K211">
-        <v>1971</v>
       </c>
       <c r="M211" t="s">
         <v>229</v>
@@ -10308,10 +10321,10 @@
     </row>
     <row r="212" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="B212" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="C212" t="s">
         <v>16</v>
@@ -10332,13 +10345,13 @@
         <v>520</v>
       </c>
       <c r="I212">
-        <v>1970</v>
+        <v>1971</v>
       </c>
       <c r="J212">
         <v>2015</v>
       </c>
       <c r="K212">
-        <v>1970</v>
+        <v>1971</v>
       </c>
       <c r="M212" t="s">
         <v>229</v>
@@ -10349,34 +10362,37 @@
     </row>
     <row r="213" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="B213" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="C213" t="s">
-        <v>186</v>
+        <v>16</v>
       </c>
       <c r="D213" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="E213" t="s">
         <v>275</v>
       </c>
       <c r="F213" t="s">
-        <v>275</v>
+        <v>17</v>
       </c>
       <c r="G213" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="H213" t="s">
         <v>520</v>
       </c>
-      <c r="I213" t="s">
-        <v>9</v>
-      </c>
-      <c r="J213" t="s">
-        <v>9</v>
+      <c r="I213">
+        <v>1970</v>
+      </c>
+      <c r="J213">
+        <v>2015</v>
+      </c>
+      <c r="K213">
+        <v>1970</v>
       </c>
       <c r="M213" t="s">
         <v>229</v>
@@ -10387,22 +10403,22 @@
     </row>
     <row r="214" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
-        <v>593</v>
+        <v>512</v>
       </c>
       <c r="B214" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="C214" t="s">
-        <v>259</v>
+        <v>186</v>
       </c>
       <c r="D214" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="E214" t="s">
         <v>275</v>
       </c>
       <c r="F214" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="G214" t="s">
         <v>17</v>
@@ -10425,13 +10441,13 @@
     </row>
     <row r="215" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
-        <v>513</v>
+        <v>593</v>
       </c>
       <c r="B215" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="C215" t="s">
-        <v>159</v>
+        <v>259</v>
       </c>
       <c r="D215" t="s">
         <v>29</v>
@@ -10440,22 +10456,19 @@
         <v>275</v>
       </c>
       <c r="F215" t="s">
-        <v>17</v>
+        <v>276</v>
       </c>
       <c r="G215" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="H215" t="s">
         <v>520</v>
       </c>
-      <c r="I215">
-        <v>2000</v>
-      </c>
-      <c r="J215">
-        <v>2015</v>
-      </c>
-      <c r="K215">
-        <v>2000</v>
+      <c r="I215" t="s">
+        <v>9</v>
+      </c>
+      <c r="J215" t="s">
+        <v>9</v>
       </c>
       <c r="M215" t="s">
         <v>229</v>
@@ -10466,34 +10479,37 @@
     </row>
     <row r="216" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="B216" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="C216" t="s">
         <v>159</v>
       </c>
       <c r="D216" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="E216" t="s">
         <v>275</v>
       </c>
       <c r="F216" t="s">
-        <v>275</v>
+        <v>17</v>
       </c>
       <c r="G216" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="H216" t="s">
         <v>520</v>
       </c>
-      <c r="I216" t="s">
-        <v>9</v>
-      </c>
-      <c r="J216" t="s">
-        <v>9</v>
+      <c r="I216">
+        <v>2000</v>
+      </c>
+      <c r="J216">
+        <v>2015</v>
+      </c>
+      <c r="K216">
+        <v>2000</v>
       </c>
       <c r="M216" t="s">
         <v>229</v>
@@ -10504,25 +10520,25 @@
     </row>
     <row r="217" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="B217" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="C217" t="s">
-        <v>35</v>
+        <v>159</v>
       </c>
       <c r="D217" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="E217" t="s">
         <v>275</v>
       </c>
       <c r="F217" t="s">
-        <v>17</v>
+        <v>275</v>
       </c>
       <c r="G217" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="H217" t="s">
         <v>520</v>
@@ -10533,9 +10549,6 @@
       <c r="J217" t="s">
         <v>9</v>
       </c>
-      <c r="K217">
-        <v>2000</v>
-      </c>
       <c r="M217" t="s">
         <v>229</v>
       </c>
@@ -10545,13 +10558,13 @@
     </row>
     <row r="218" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="B218" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="C218" t="s">
-        <v>278</v>
+        <v>35</v>
       </c>
       <c r="D218" t="s">
         <v>29</v>
@@ -10586,10 +10599,10 @@
     </row>
     <row r="219" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="B219" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="C219" t="s">
         <v>278</v>
@@ -10627,10 +10640,10 @@
     </row>
     <row r="220" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="B220" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="C220" t="s">
         <v>278</v>
@@ -10668,13 +10681,13 @@
     </row>
     <row r="221" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
-        <v>567</v>
+        <v>518</v>
       </c>
       <c r="B221" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="C221" t="s">
-        <v>564</v>
+        <v>278</v>
       </c>
       <c r="D221" t="s">
         <v>29</v>
@@ -10691,28 +10704,34 @@
       <c r="H221" t="s">
         <v>520</v>
       </c>
-      <c r="I221">
-        <v>2000</v>
-      </c>
-      <c r="J221">
-        <v>2015</v>
+      <c r="I221" t="s">
+        <v>9</v>
+      </c>
+      <c r="J221" t="s">
+        <v>9</v>
       </c>
       <c r="K221">
         <v>2000</v>
       </c>
+      <c r="M221" t="s">
+        <v>229</v>
+      </c>
+      <c r="N221" t="s">
+        <v>229</v>
+      </c>
     </row>
     <row r="222" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="B222" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="C222" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="D222" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="E222" t="s">
         <v>275</v>
@@ -10738,13 +10757,16 @@
     </row>
     <row r="223" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
-        <v>519</v>
+        <v>568</v>
       </c>
       <c r="B223" t="s">
-        <v>644</v>
+        <v>643</v>
+      </c>
+      <c r="C223" t="s">
+        <v>563</v>
       </c>
       <c r="D223" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="E223" t="s">
         <v>275</v>
@@ -10758,31 +10780,22 @@
       <c r="H223" t="s">
         <v>520</v>
       </c>
-      <c r="I223" t="s">
-        <v>9</v>
-      </c>
-      <c r="J223" t="s">
-        <v>9</v>
+      <c r="I223">
+        <v>2000</v>
+      </c>
+      <c r="J223">
+        <v>2015</v>
       </c>
       <c r="K223">
         <v>2000</v>
       </c>
-      <c r="M223" t="s">
-        <v>229</v>
-      </c>
-      <c r="N223" t="s">
-        <v>229</v>
-      </c>
     </row>
     <row r="224" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
-        <v>581</v>
+        <v>519</v>
       </c>
       <c r="B224" t="s">
-        <v>645</v>
-      </c>
-      <c r="C224" t="s">
-        <v>16</v>
+        <v>644</v>
       </c>
       <c r="D224" t="s">
         <v>29</v>
@@ -10799,19 +10812,31 @@
       <c r="H224" t="s">
         <v>520</v>
       </c>
+      <c r="I224" t="s">
+        <v>9</v>
+      </c>
+      <c r="J224" t="s">
+        <v>9</v>
+      </c>
       <c r="K224">
         <v>2000</v>
       </c>
+      <c r="M224" t="s">
+        <v>229</v>
+      </c>
+      <c r="N224" t="s">
+        <v>229</v>
+      </c>
     </row>
     <row r="225" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="B225" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="C225" t="s">
-        <v>159</v>
+        <v>16</v>
       </c>
       <c r="D225" t="s">
         <v>29</v>
@@ -10834,10 +10859,10 @@
     </row>
     <row r="226" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="B226" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="C226" t="s">
         <v>159</v>
@@ -10863,13 +10888,13 @@
     </row>
     <row r="227" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
-        <v>522</v>
+        <v>583</v>
       </c>
       <c r="B227" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="C227" t="s">
-        <v>35</v>
+        <v>159</v>
       </c>
       <c r="D227" t="s">
         <v>29</v>
@@ -10884,33 +10909,21 @@
         <v>8</v>
       </c>
       <c r="H227" t="s">
-        <v>521</v>
-      </c>
-      <c r="I227">
-        <v>1970</v>
-      </c>
-      <c r="J227">
-        <v>2015</v>
+        <v>520</v>
       </c>
       <c r="K227">
-        <v>1970</v>
-      </c>
-      <c r="M227" t="s">
-        <v>229</v>
-      </c>
-      <c r="N227" t="s">
-        <v>229</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="228" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="B228" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="C228" t="s">
-        <v>159</v>
+        <v>35</v>
       </c>
       <c r="D228" t="s">
         <v>29</v>
@@ -10927,17 +10940,14 @@
       <c r="H228" t="s">
         <v>521</v>
       </c>
-      <c r="I228" t="s">
-        <v>9</v>
-      </c>
-      <c r="J228" t="s">
-        <v>9</v>
+      <c r="I228">
+        <v>1970</v>
+      </c>
+      <c r="J228">
+        <v>2015</v>
       </c>
       <c r="K228">
-        <v>2015</v>
-      </c>
-      <c r="L228" t="s">
-        <v>9</v>
+        <v>1970</v>
       </c>
       <c r="M228" t="s">
         <v>229</v>
@@ -10948,16 +10958,16 @@
     </row>
     <row r="229" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="B229" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="C229" t="s">
-        <v>16</v>
+        <v>159</v>
       </c>
       <c r="D229" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="E229" t="s">
         <v>275</v>
@@ -10980,6 +10990,9 @@
       <c r="K229">
         <v>2015</v>
       </c>
+      <c r="L229" t="s">
+        <v>9</v>
+      </c>
       <c r="M229" t="s">
         <v>229</v>
       </c>
@@ -10989,16 +11002,16 @@
     </row>
     <row r="230" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="B230" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="C230" t="s">
         <v>16</v>
       </c>
       <c r="D230" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="E230" t="s">
         <v>275</v>
@@ -11012,14 +11025,14 @@
       <c r="H230" t="s">
         <v>521</v>
       </c>
-      <c r="I230">
-        <v>1971</v>
-      </c>
-      <c r="J230">
+      <c r="I230" t="s">
+        <v>9</v>
+      </c>
+      <c r="J230" t="s">
+        <v>9</v>
+      </c>
+      <c r="K230">
         <v>2015</v>
-      </c>
-      <c r="K230">
-        <v>1971</v>
       </c>
       <c r="M230" t="s">
         <v>229</v>
@@ -11030,10 +11043,10 @@
     </row>
     <row r="231" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="B231" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="C231" t="s">
         <v>16</v>
@@ -11054,13 +11067,13 @@
         <v>521</v>
       </c>
       <c r="I231">
-        <v>1970</v>
+        <v>1971</v>
       </c>
       <c r="J231">
         <v>2015</v>
       </c>
       <c r="K231">
-        <v>1970</v>
+        <v>1971</v>
       </c>
       <c r="M231" t="s">
         <v>229</v>
@@ -11071,34 +11084,37 @@
     </row>
     <row r="232" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="B232" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="C232" t="s">
-        <v>186</v>
+        <v>16</v>
       </c>
       <c r="D232" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="E232" t="s">
         <v>275</v>
       </c>
       <c r="F232" t="s">
-        <v>275</v>
+        <v>17</v>
       </c>
       <c r="G232" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="H232" t="s">
         <v>521</v>
       </c>
-      <c r="I232" t="s">
-        <v>9</v>
-      </c>
-      <c r="J232" t="s">
-        <v>9</v>
+      <c r="I232">
+        <v>1970</v>
+      </c>
+      <c r="J232">
+        <v>2015</v>
+      </c>
+      <c r="K232">
+        <v>1970</v>
       </c>
       <c r="M232" t="s">
         <v>229</v>
@@ -11109,22 +11125,22 @@
     </row>
     <row r="233" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
-        <v>594</v>
+        <v>527</v>
       </c>
       <c r="B233" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="C233" t="s">
-        <v>259</v>
+        <v>186</v>
       </c>
       <c r="D233" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="E233" t="s">
         <v>275</v>
       </c>
       <c r="F233" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="G233" t="s">
         <v>17</v>
@@ -11147,13 +11163,13 @@
     </row>
     <row r="234" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
-        <v>528</v>
+        <v>594</v>
       </c>
       <c r="B234" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="C234" t="s">
-        <v>159</v>
+        <v>259</v>
       </c>
       <c r="D234" t="s">
         <v>29</v>
@@ -11162,22 +11178,19 @@
         <v>275</v>
       </c>
       <c r="F234" t="s">
-        <v>17</v>
+        <v>276</v>
       </c>
       <c r="G234" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="H234" t="s">
         <v>521</v>
       </c>
-      <c r="I234">
-        <v>2000</v>
-      </c>
-      <c r="J234">
-        <v>2015</v>
-      </c>
-      <c r="K234">
-        <v>2000</v>
+      <c r="I234" t="s">
+        <v>9</v>
+      </c>
+      <c r="J234" t="s">
+        <v>9</v>
       </c>
       <c r="M234" t="s">
         <v>229</v>
@@ -11188,34 +11201,37 @@
     </row>
     <row r="235" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="B235" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="C235" t="s">
         <v>159</v>
       </c>
       <c r="D235" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="E235" t="s">
         <v>275</v>
       </c>
       <c r="F235" t="s">
-        <v>275</v>
+        <v>17</v>
       </c>
       <c r="G235" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="H235" t="s">
         <v>521</v>
       </c>
-      <c r="I235" t="s">
-        <v>9</v>
-      </c>
-      <c r="J235" t="s">
-        <v>9</v>
+      <c r="I235">
+        <v>2000</v>
+      </c>
+      <c r="J235">
+        <v>2015</v>
+      </c>
+      <c r="K235">
+        <v>2000</v>
       </c>
       <c r="M235" t="s">
         <v>229</v>
@@ -11226,25 +11242,25 @@
     </row>
     <row r="236" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="B236" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="C236" t="s">
-        <v>35</v>
+        <v>159</v>
       </c>
       <c r="D236" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="E236" t="s">
         <v>275</v>
       </c>
       <c r="F236" t="s">
-        <v>17</v>
+        <v>275</v>
       </c>
       <c r="G236" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="H236" t="s">
         <v>521</v>
@@ -11255,9 +11271,6 @@
       <c r="J236" t="s">
         <v>9</v>
       </c>
-      <c r="K236">
-        <v>2000</v>
-      </c>
       <c r="M236" t="s">
         <v>229</v>
       </c>
@@ -11267,13 +11280,13 @@
     </row>
     <row r="237" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="B237" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="C237" t="s">
-        <v>278</v>
+        <v>35</v>
       </c>
       <c r="D237" t="s">
         <v>29</v>
@@ -11308,10 +11321,10 @@
     </row>
     <row r="238" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="B238" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="C238" t="s">
         <v>278</v>
@@ -11349,10 +11362,10 @@
     </row>
     <row r="239" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="B239" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="C239" t="s">
         <v>278</v>
@@ -11390,13 +11403,13 @@
     </row>
     <row r="240" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
-        <v>569</v>
+        <v>533</v>
       </c>
       <c r="B240" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="C240" t="s">
-        <v>564</v>
+        <v>278</v>
       </c>
       <c r="D240" t="s">
         <v>29</v>
@@ -11413,28 +11426,34 @@
       <c r="H240" t="s">
         <v>521</v>
       </c>
-      <c r="I240">
-        <v>2000</v>
-      </c>
-      <c r="J240">
-        <v>2015</v>
+      <c r="I240" t="s">
+        <v>9</v>
+      </c>
+      <c r="J240" t="s">
+        <v>9</v>
       </c>
       <c r="K240">
         <v>2000</v>
       </c>
+      <c r="M240" t="s">
+        <v>229</v>
+      </c>
+      <c r="N240" t="s">
+        <v>229</v>
+      </c>
     </row>
     <row r="241" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="B241" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="C241" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="D241" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="E241" t="s">
         <v>275</v>
@@ -11460,13 +11479,16 @@
     </row>
     <row r="242" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
-        <v>534</v>
+        <v>570</v>
       </c>
       <c r="B242" t="s">
-        <v>663</v>
+        <v>662</v>
+      </c>
+      <c r="C242" t="s">
+        <v>563</v>
       </c>
       <c r="D242" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="E242" t="s">
         <v>275</v>
@@ -11480,31 +11502,22 @@
       <c r="H242" t="s">
         <v>521</v>
       </c>
-      <c r="I242" t="s">
-        <v>9</v>
-      </c>
-      <c r="J242" t="s">
-        <v>9</v>
+      <c r="I242">
+        <v>2000</v>
+      </c>
+      <c r="J242">
+        <v>2015</v>
       </c>
       <c r="K242">
         <v>2000</v>
       </c>
-      <c r="M242" t="s">
-        <v>229</v>
-      </c>
-      <c r="N242" t="s">
-        <v>229</v>
-      </c>
     </row>
     <row r="243" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
-        <v>584</v>
+        <v>534</v>
       </c>
       <c r="B243" t="s">
-        <v>664</v>
-      </c>
-      <c r="C243" t="s">
-        <v>16</v>
+        <v>663</v>
       </c>
       <c r="D243" t="s">
         <v>29</v>
@@ -11521,19 +11534,31 @@
       <c r="H243" t="s">
         <v>521</v>
       </c>
+      <c r="I243" t="s">
+        <v>9</v>
+      </c>
+      <c r="J243" t="s">
+        <v>9</v>
+      </c>
       <c r="K243">
         <v>2000</v>
       </c>
+      <c r="M243" t="s">
+        <v>229</v>
+      </c>
+      <c r="N243" t="s">
+        <v>229</v>
+      </c>
     </row>
     <row r="244" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B244" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="C244" t="s">
-        <v>159</v>
+        <v>16</v>
       </c>
       <c r="D244" t="s">
         <v>29</v>
@@ -11556,10 +11581,10 @@
     </row>
     <row r="245" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="B245" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="C245" t="s">
         <v>159</v>
@@ -11585,13 +11610,13 @@
     </row>
     <row r="246" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
-        <v>535</v>
+        <v>586</v>
       </c>
       <c r="B246" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="C246" t="s">
-        <v>35</v>
+        <v>159</v>
       </c>
       <c r="D246" t="s">
         <v>29</v>
@@ -11606,33 +11631,21 @@
         <v>8</v>
       </c>
       <c r="H246" t="s">
-        <v>548</v>
-      </c>
-      <c r="I246">
-        <v>1970</v>
-      </c>
-      <c r="J246">
-        <v>2015</v>
+        <v>521</v>
       </c>
       <c r="K246">
-        <v>1970</v>
-      </c>
-      <c r="M246" t="s">
-        <v>229</v>
-      </c>
-      <c r="N246" t="s">
-        <v>229</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="247" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="B247" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="C247" t="s">
-        <v>159</v>
+        <v>35</v>
       </c>
       <c r="D247" t="s">
         <v>29</v>
@@ -11649,17 +11662,14 @@
       <c r="H247" t="s">
         <v>548</v>
       </c>
-      <c r="I247" t="s">
-        <v>9</v>
-      </c>
-      <c r="J247" t="s">
-        <v>9</v>
+      <c r="I247">
+        <v>1970</v>
+      </c>
+      <c r="J247">
+        <v>2015</v>
       </c>
       <c r="K247">
-        <v>2015</v>
-      </c>
-      <c r="L247" t="s">
-        <v>9</v>
+        <v>1970</v>
       </c>
       <c r="M247" t="s">
         <v>229</v>
@@ -11670,16 +11680,16 @@
     </row>
     <row r="248" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="B248" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="C248" t="s">
-        <v>16</v>
+        <v>159</v>
       </c>
       <c r="D248" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="E248" t="s">
         <v>275</v>
@@ -11702,6 +11712,9 @@
       <c r="K248">
         <v>2015</v>
       </c>
+      <c r="L248" t="s">
+        <v>9</v>
+      </c>
       <c r="M248" t="s">
         <v>229</v>
       </c>
@@ -11711,16 +11724,16 @@
     </row>
     <row r="249" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="B249" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="C249" t="s">
         <v>16</v>
       </c>
       <c r="D249" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="E249" t="s">
         <v>275</v>
@@ -11734,14 +11747,14 @@
       <c r="H249" t="s">
         <v>548</v>
       </c>
-      <c r="I249">
-        <v>1971</v>
-      </c>
-      <c r="J249">
+      <c r="I249" t="s">
+        <v>9</v>
+      </c>
+      <c r="J249" t="s">
+        <v>9</v>
+      </c>
+      <c r="K249">
         <v>2015</v>
-      </c>
-      <c r="K249">
-        <v>1971</v>
       </c>
       <c r="M249" t="s">
         <v>229</v>
@@ -11752,10 +11765,10 @@
     </row>
     <row r="250" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="B250" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="C250" t="s">
         <v>16</v>
@@ -11776,13 +11789,13 @@
         <v>548</v>
       </c>
       <c r="I250">
-        <v>1970</v>
+        <v>1971</v>
       </c>
       <c r="J250">
         <v>2015</v>
       </c>
       <c r="K250">
-        <v>1970</v>
+        <v>1971</v>
       </c>
       <c r="M250" t="s">
         <v>229</v>
@@ -11793,34 +11806,37 @@
     </row>
     <row r="251" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="B251" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="C251" t="s">
-        <v>186</v>
+        <v>16</v>
       </c>
       <c r="D251" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="E251" t="s">
         <v>275</v>
       </c>
       <c r="F251" t="s">
-        <v>275</v>
+        <v>17</v>
       </c>
       <c r="G251" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="H251" t="s">
         <v>548</v>
       </c>
-      <c r="I251" t="s">
-        <v>9</v>
-      </c>
-      <c r="J251" t="s">
-        <v>9</v>
+      <c r="I251">
+        <v>1970</v>
+      </c>
+      <c r="J251">
+        <v>2015</v>
+      </c>
+      <c r="K251">
+        <v>1970</v>
       </c>
       <c r="M251" t="s">
         <v>229</v>
@@ -11831,22 +11847,22 @@
     </row>
     <row r="252" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
-        <v>595</v>
+        <v>540</v>
       </c>
       <c r="B252" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="C252" t="s">
-        <v>259</v>
+        <v>186</v>
       </c>
       <c r="D252" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="E252" t="s">
         <v>275</v>
       </c>
       <c r="F252" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="G252" t="s">
         <v>17</v>
@@ -11869,13 +11885,13 @@
     </row>
     <row r="253" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
-        <v>541</v>
+        <v>595</v>
       </c>
       <c r="B253" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="C253" t="s">
-        <v>159</v>
+        <v>259</v>
       </c>
       <c r="D253" t="s">
         <v>29</v>
@@ -11884,22 +11900,19 @@
         <v>275</v>
       </c>
       <c r="F253" t="s">
-        <v>17</v>
+        <v>276</v>
       </c>
       <c r="G253" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="H253" t="s">
         <v>548</v>
       </c>
-      <c r="I253">
-        <v>2000</v>
-      </c>
-      <c r="J253">
-        <v>2015</v>
-      </c>
-      <c r="K253">
-        <v>2000</v>
+      <c r="I253" t="s">
+        <v>9</v>
+      </c>
+      <c r="J253" t="s">
+        <v>9</v>
       </c>
       <c r="M253" t="s">
         <v>229</v>
@@ -11910,34 +11923,37 @@
     </row>
     <row r="254" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="B254" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="C254" t="s">
         <v>159</v>
       </c>
       <c r="D254" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="E254" t="s">
         <v>275</v>
       </c>
       <c r="F254" t="s">
-        <v>275</v>
+        <v>17</v>
       </c>
       <c r="G254" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="H254" t="s">
         <v>548</v>
       </c>
-      <c r="I254" t="s">
-        <v>9</v>
-      </c>
-      <c r="J254" t="s">
-        <v>9</v>
+      <c r="I254">
+        <v>2000</v>
+      </c>
+      <c r="J254">
+        <v>2015</v>
+      </c>
+      <c r="K254">
+        <v>2000</v>
       </c>
       <c r="M254" t="s">
         <v>229</v>
@@ -11948,25 +11964,25 @@
     </row>
     <row r="255" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="B255" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="C255" t="s">
-        <v>35</v>
+        <v>159</v>
       </c>
       <c r="D255" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="E255" t="s">
         <v>275</v>
       </c>
       <c r="F255" t="s">
-        <v>17</v>
+        <v>275</v>
       </c>
       <c r="G255" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="H255" t="s">
         <v>548</v>
@@ -11977,9 +11993,6 @@
       <c r="J255" t="s">
         <v>9</v>
       </c>
-      <c r="K255">
-        <v>2000</v>
-      </c>
       <c r="M255" t="s">
         <v>229</v>
       </c>
@@ -11989,13 +12002,13 @@
     </row>
     <row r="256" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="B256" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="C256" t="s">
-        <v>278</v>
+        <v>35</v>
       </c>
       <c r="D256" t="s">
         <v>29</v>
@@ -12030,10 +12043,10 @@
     </row>
     <row r="257" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="B257" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="C257" t="s">
         <v>278</v>
@@ -12071,10 +12084,10 @@
     </row>
     <row r="258" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="B258" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="C258" t="s">
         <v>278</v>
@@ -12112,13 +12125,13 @@
     </row>
     <row r="259" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
-        <v>571</v>
+        <v>546</v>
       </c>
       <c r="B259" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="C259" t="s">
-        <v>564</v>
+        <v>278</v>
       </c>
       <c r="D259" t="s">
         <v>29</v>
@@ -12135,28 +12148,34 @@
       <c r="H259" t="s">
         <v>548</v>
       </c>
-      <c r="I259">
-        <v>2000</v>
-      </c>
-      <c r="J259">
-        <v>2015</v>
+      <c r="I259" t="s">
+        <v>9</v>
+      </c>
+      <c r="J259" t="s">
+        <v>9</v>
       </c>
       <c r="K259">
         <v>2000</v>
       </c>
+      <c r="M259" t="s">
+        <v>229</v>
+      </c>
+      <c r="N259" t="s">
+        <v>229</v>
+      </c>
     </row>
     <row r="260" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="B260" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="C260" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="D260" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="E260" t="s">
         <v>275</v>
@@ -12182,13 +12201,16 @@
     </row>
     <row r="261" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
-        <v>547</v>
+        <v>572</v>
       </c>
       <c r="B261" t="s">
-        <v>682</v>
+        <v>681</v>
+      </c>
+      <c r="C261" t="s">
+        <v>563</v>
       </c>
       <c r="D261" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="E261" t="s">
         <v>275</v>
@@ -12202,31 +12224,22 @@
       <c r="H261" t="s">
         <v>548</v>
       </c>
-      <c r="I261" t="s">
-        <v>9</v>
-      </c>
-      <c r="J261" t="s">
-        <v>9</v>
+      <c r="I261">
+        <v>2000</v>
+      </c>
+      <c r="J261">
+        <v>2015</v>
       </c>
       <c r="K261">
         <v>2000</v>
       </c>
-      <c r="M261" t="s">
-        <v>229</v>
-      </c>
-      <c r="N261" t="s">
-        <v>229</v>
-      </c>
     </row>
     <row r="262" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
-        <v>587</v>
+        <v>547</v>
       </c>
       <c r="B262" t="s">
-        <v>683</v>
-      </c>
-      <c r="C262" t="s">
-        <v>16</v>
+        <v>682</v>
       </c>
       <c r="D262" t="s">
         <v>29</v>
@@ -12243,19 +12256,31 @@
       <c r="H262" t="s">
         <v>548</v>
       </c>
+      <c r="I262" t="s">
+        <v>9</v>
+      </c>
+      <c r="J262" t="s">
+        <v>9</v>
+      </c>
       <c r="K262">
         <v>2000</v>
       </c>
+      <c r="M262" t="s">
+        <v>229</v>
+      </c>
+      <c r="N262" t="s">
+        <v>229</v>
+      </c>
     </row>
     <row r="263" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="B263" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="C263" t="s">
-        <v>159</v>
+        <v>16</v>
       </c>
       <c r="D263" t="s">
         <v>29</v>
@@ -12278,10 +12303,10 @@
     </row>
     <row r="264" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="B264" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="C264" t="s">
         <v>159</v>
@@ -12307,13 +12332,13 @@
     </row>
     <row r="265" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
-        <v>550</v>
+        <v>589</v>
       </c>
       <c r="B265" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="C265" t="s">
-        <v>35</v>
+        <v>159</v>
       </c>
       <c r="D265" t="s">
         <v>29</v>
@@ -12328,33 +12353,21 @@
         <v>8</v>
       </c>
       <c r="H265" t="s">
-        <v>549</v>
-      </c>
-      <c r="I265">
-        <v>1970</v>
-      </c>
-      <c r="J265">
-        <v>2015</v>
+        <v>548</v>
       </c>
       <c r="K265">
-        <v>1970</v>
-      </c>
-      <c r="M265" t="s">
-        <v>229</v>
-      </c>
-      <c r="N265" t="s">
-        <v>229</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="266" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B266" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="C266" t="s">
-        <v>159</v>
+        <v>35</v>
       </c>
       <c r="D266" t="s">
         <v>29</v>
@@ -12371,17 +12384,14 @@
       <c r="H266" t="s">
         <v>549</v>
       </c>
-      <c r="I266" t="s">
-        <v>9</v>
-      </c>
-      <c r="J266" t="s">
-        <v>9</v>
+      <c r="I266">
+        <v>1970</v>
+      </c>
+      <c r="J266">
+        <v>2015</v>
       </c>
       <c r="K266">
-        <v>2015</v>
-      </c>
-      <c r="L266" t="s">
-        <v>9</v>
+        <v>1970</v>
       </c>
       <c r="M266" t="s">
         <v>229</v>
@@ -12392,16 +12402,16 @@
     </row>
     <row r="267" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="B267" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="C267" t="s">
-        <v>16</v>
+        <v>159</v>
       </c>
       <c r="D267" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="E267" t="s">
         <v>275</v>
@@ -12424,6 +12434,9 @@
       <c r="K267">
         <v>2015</v>
       </c>
+      <c r="L267" t="s">
+        <v>9</v>
+      </c>
       <c r="M267" t="s">
         <v>229</v>
       </c>
@@ -12433,16 +12446,16 @@
     </row>
     <row r="268" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="B268" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="C268" t="s">
         <v>16</v>
       </c>
       <c r="D268" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="E268" t="s">
         <v>275</v>
@@ -12456,14 +12469,14 @@
       <c r="H268" t="s">
         <v>549</v>
       </c>
-      <c r="I268">
-        <v>1971</v>
-      </c>
-      <c r="J268">
+      <c r="I268" t="s">
+        <v>9</v>
+      </c>
+      <c r="J268" t="s">
+        <v>9</v>
+      </c>
+      <c r="K268">
         <v>2015</v>
-      </c>
-      <c r="K268">
-        <v>1971</v>
       </c>
       <c r="M268" t="s">
         <v>229</v>
@@ -12474,10 +12487,10 @@
     </row>
     <row r="269" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="B269" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="C269" t="s">
         <v>16</v>
@@ -12498,13 +12511,13 @@
         <v>549</v>
       </c>
       <c r="I269">
-        <v>1970</v>
+        <v>1971</v>
       </c>
       <c r="J269">
         <v>2015</v>
       </c>
       <c r="K269">
-        <v>1970</v>
+        <v>1971</v>
       </c>
       <c r="M269" t="s">
         <v>229</v>
@@ -12515,34 +12528,37 @@
     </row>
     <row r="270" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="B270" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="C270" t="s">
-        <v>186</v>
+        <v>16</v>
       </c>
       <c r="D270" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="E270" t="s">
         <v>275</v>
       </c>
       <c r="F270" t="s">
-        <v>275</v>
+        <v>17</v>
       </c>
       <c r="G270" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="H270" t="s">
         <v>549</v>
       </c>
-      <c r="I270" t="s">
-        <v>9</v>
-      </c>
-      <c r="J270" t="s">
-        <v>9</v>
+      <c r="I270">
+        <v>1970</v>
+      </c>
+      <c r="J270">
+        <v>2015</v>
+      </c>
+      <c r="K270">
+        <v>1970</v>
       </c>
       <c r="M270" t="s">
         <v>229</v>
@@ -12553,22 +12569,22 @@
     </row>
     <row r="271" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
-        <v>596</v>
+        <v>555</v>
       </c>
       <c r="B271" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="C271" t="s">
-        <v>259</v>
+        <v>186</v>
       </c>
       <c r="D271" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="E271" t="s">
         <v>275</v>
       </c>
       <c r="F271" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="G271" t="s">
         <v>17</v>
@@ -12591,13 +12607,13 @@
     </row>
     <row r="272" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
-        <v>556</v>
+        <v>596</v>
       </c>
       <c r="B272" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="C272" t="s">
-        <v>159</v>
+        <v>259</v>
       </c>
       <c r="D272" t="s">
         <v>29</v>
@@ -12606,22 +12622,19 @@
         <v>275</v>
       </c>
       <c r="F272" t="s">
-        <v>17</v>
+        <v>276</v>
       </c>
       <c r="G272" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="H272" t="s">
         <v>549</v>
       </c>
-      <c r="I272">
-        <v>2000</v>
-      </c>
-      <c r="J272">
-        <v>2015</v>
-      </c>
-      <c r="K272">
-        <v>2000</v>
+      <c r="I272" t="s">
+        <v>9</v>
+      </c>
+      <c r="J272" t="s">
+        <v>9</v>
       </c>
       <c r="M272" t="s">
         <v>229</v>
@@ -12632,34 +12645,37 @@
     </row>
     <row r="273" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="B273" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="C273" t="s">
         <v>159</v>
       </c>
       <c r="D273" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="E273" t="s">
         <v>275</v>
       </c>
       <c r="F273" t="s">
-        <v>275</v>
+        <v>17</v>
       </c>
       <c r="G273" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="H273" t="s">
         <v>549</v>
       </c>
-      <c r="I273" t="s">
-        <v>9</v>
-      </c>
-      <c r="J273" t="s">
-        <v>9</v>
+      <c r="I273">
+        <v>2000</v>
+      </c>
+      <c r="J273">
+        <v>2015</v>
+      </c>
+      <c r="K273">
+        <v>2000</v>
       </c>
       <c r="M273" t="s">
         <v>229</v>
@@ -12670,25 +12686,25 @@
     </row>
     <row r="274" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="B274" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="C274" t="s">
-        <v>35</v>
+        <v>159</v>
       </c>
       <c r="D274" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="E274" t="s">
         <v>275</v>
       </c>
       <c r="F274" t="s">
-        <v>17</v>
+        <v>275</v>
       </c>
       <c r="G274" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="H274" t="s">
         <v>549</v>
@@ -12699,9 +12715,6 @@
       <c r="J274" t="s">
         <v>9</v>
       </c>
-      <c r="K274">
-        <v>2000</v>
-      </c>
       <c r="M274" t="s">
         <v>229</v>
       </c>
@@ -12711,13 +12724,13 @@
     </row>
     <row r="275" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="B275" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="C275" t="s">
-        <v>278</v>
+        <v>35</v>
       </c>
       <c r="D275" t="s">
         <v>29</v>
@@ -12752,10 +12765,10 @@
     </row>
     <row r="276" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="B276" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="C276" t="s">
         <v>278</v>
@@ -12793,10 +12806,10 @@
     </row>
     <row r="277" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="B277" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="C277" t="s">
         <v>278</v>
@@ -12834,13 +12847,13 @@
     </row>
     <row r="278" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
-        <v>573</v>
+        <v>561</v>
       </c>
       <c r="B278" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="C278" t="s">
-        <v>564</v>
+        <v>278</v>
       </c>
       <c r="D278" t="s">
         <v>29</v>
@@ -12857,28 +12870,34 @@
       <c r="H278" t="s">
         <v>549</v>
       </c>
-      <c r="I278">
-        <v>2000</v>
-      </c>
-      <c r="J278">
-        <v>2015</v>
+      <c r="I278" t="s">
+        <v>9</v>
+      </c>
+      <c r="J278" t="s">
+        <v>9</v>
       </c>
       <c r="K278">
         <v>2000</v>
       </c>
+      <c r="M278" t="s">
+        <v>229</v>
+      </c>
+      <c r="N278" t="s">
+        <v>229</v>
+      </c>
     </row>
     <row r="279" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="B279" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="C279" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="D279" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="E279" t="s">
         <v>275</v>
@@ -12904,13 +12923,16 @@
     </row>
     <row r="280" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
-        <v>562</v>
+        <v>574</v>
       </c>
       <c r="B280" t="s">
-        <v>701</v>
+        <v>700</v>
+      </c>
+      <c r="C280" t="s">
+        <v>563</v>
       </c>
       <c r="D280" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="E280" t="s">
         <v>275</v>
@@ -12924,31 +12946,22 @@
       <c r="H280" t="s">
         <v>549</v>
       </c>
-      <c r="I280" t="s">
-        <v>9</v>
-      </c>
-      <c r="J280" t="s">
-        <v>9</v>
+      <c r="I280">
+        <v>2000</v>
+      </c>
+      <c r="J280">
+        <v>2015</v>
       </c>
       <c r="K280">
         <v>2000</v>
       </c>
-      <c r="M280" t="s">
-        <v>229</v>
-      </c>
-      <c r="N280" t="s">
-        <v>229</v>
-      </c>
     </row>
     <row r="281" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
-        <v>575</v>
+        <v>562</v>
       </c>
       <c r="B281" t="s">
-        <v>702</v>
-      </c>
-      <c r="C281" t="s">
-        <v>16</v>
+        <v>701</v>
       </c>
       <c r="D281" t="s">
         <v>29</v>
@@ -12965,19 +12978,31 @@
       <c r="H281" t="s">
         <v>549</v>
       </c>
+      <c r="I281" t="s">
+        <v>9</v>
+      </c>
+      <c r="J281" t="s">
+        <v>9</v>
+      </c>
       <c r="K281">
         <v>2000</v>
       </c>
+      <c r="M281" t="s">
+        <v>229</v>
+      </c>
+      <c r="N281" t="s">
+        <v>229</v>
+      </c>
     </row>
     <row r="282" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="B282" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="C282" t="s">
-        <v>159</v>
+        <v>16</v>
       </c>
       <c r="D282" t="s">
         <v>29</v>
@@ -13000,10 +13025,10 @@
     </row>
     <row r="283" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="B283" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="C283" t="s">
         <v>159</v>
@@ -13029,19 +13054,19 @@
     </row>
     <row r="284" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
-        <v>400</v>
+        <v>577</v>
       </c>
       <c r="B284" t="s">
-        <v>401</v>
+        <v>704</v>
       </c>
       <c r="C284" t="s">
-        <v>402</v>
+        <v>159</v>
       </c>
       <c r="D284" t="s">
         <v>29</v>
       </c>
       <c r="E284" t="s">
-        <v>17</v>
+        <v>275</v>
       </c>
       <c r="F284" t="s">
         <v>17</v>
@@ -13050,30 +13075,21 @@
         <v>8</v>
       </c>
       <c r="H284" t="s">
-        <v>403</v>
-      </c>
-      <c r="J284">
-        <v>2018</v>
+        <v>549</v>
       </c>
       <c r="K284">
-        <v>1995</v>
-      </c>
-      <c r="M284" t="s">
-        <v>229</v>
-      </c>
-      <c r="N284" t="s">
-        <v>229</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="285" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
-        <v>404</v>
+        <v>400</v>
       </c>
       <c r="B285" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="C285" t="s">
-        <v>608</v>
+        <v>402</v>
       </c>
       <c r="D285" t="s">
         <v>29</v>
@@ -13091,7 +13107,7 @@
         <v>403</v>
       </c>
       <c r="J285">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="K285">
         <v>1995</v>
@@ -13105,19 +13121,19 @@
     </row>
     <row r="286" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="B286" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="C286" t="s">
-        <v>159</v>
+        <v>608</v>
       </c>
       <c r="D286" t="s">
         <v>29</v>
       </c>
       <c r="E286" t="s">
-        <v>408</v>
+        <v>17</v>
       </c>
       <c r="F286" t="s">
         <v>17</v>
@@ -13132,7 +13148,7 @@
         <v>2019</v>
       </c>
       <c r="K286">
-        <v>2001</v>
+        <v>1995</v>
       </c>
       <c r="M286" t="s">
         <v>229</v>
@@ -13143,19 +13159,19 @@
     </row>
     <row r="287" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="B287" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="C287" t="s">
-        <v>411</v>
+        <v>159</v>
       </c>
       <c r="D287" t="s">
         <v>29</v>
       </c>
       <c r="E287" t="s">
-        <v>17</v>
+        <v>408</v>
       </c>
       <c r="F287" t="s">
         <v>17</v>
@@ -13170,7 +13186,7 @@
         <v>2019</v>
       </c>
       <c r="K287">
-        <v>1995</v>
+        <v>2001</v>
       </c>
       <c r="M287" t="s">
         <v>229</v>
@@ -13181,13 +13197,13 @@
     </row>
     <row r="288" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="B288" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="C288" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="D288" t="s">
         <v>29</v>
@@ -13208,7 +13224,7 @@
         <v>2019</v>
       </c>
       <c r="K288">
-        <v>2018</v>
+        <v>1995</v>
       </c>
       <c r="M288" t="s">
         <v>229</v>
@@ -13219,16 +13235,19 @@
     </row>
     <row r="289" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="B289" t="s">
-        <v>416</v>
+        <v>413</v>
+      </c>
+      <c r="C289" t="s">
+        <v>414</v>
       </c>
       <c r="D289" t="s">
         <v>29</v>
       </c>
       <c r="E289" t="s">
-        <v>408</v>
+        <v>17</v>
       </c>
       <c r="F289" t="s">
         <v>17</v>
@@ -13254,13 +13273,10 @@
     </row>
     <row r="290" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="B290" t="s">
-        <v>418</v>
-      </c>
-      <c r="C290" t="s">
-        <v>159</v>
+        <v>416</v>
       </c>
       <c r="D290" t="s">
         <v>29</v>
@@ -13292,13 +13308,13 @@
     </row>
     <row r="291" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="B291" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="C291" t="s">
-        <v>212</v>
+        <v>159</v>
       </c>
       <c r="D291" t="s">
         <v>29</v>
@@ -13330,13 +13346,13 @@
     </row>
     <row r="292" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="B292" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="C292" t="s">
-        <v>423</v>
+        <v>212</v>
       </c>
       <c r="D292" t="s">
         <v>29</v>
@@ -13368,19 +13384,19 @@
     </row>
     <row r="293" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="B293" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="C293" t="s">
-        <v>159</v>
+        <v>423</v>
       </c>
       <c r="D293" t="s">
         <v>29</v>
       </c>
       <c r="E293" t="s">
-        <v>17</v>
+        <v>408</v>
       </c>
       <c r="F293" t="s">
         <v>17</v>
@@ -13406,13 +13422,13 @@
     </row>
     <row r="294" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B294" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="C294" t="s">
-        <v>428</v>
+        <v>159</v>
       </c>
       <c r="D294" t="s">
         <v>29</v>
@@ -13444,13 +13460,13 @@
     </row>
     <row r="295" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="B295" t="s">
-        <v>413</v>
+        <v>427</v>
       </c>
       <c r="C295" t="s">
-        <v>414</v>
+        <v>428</v>
       </c>
       <c r="D295" t="s">
         <v>29</v>
@@ -13482,26 +13498,35 @@
     </row>
     <row r="296" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="B296" t="s">
-        <v>431</v>
+        <v>413</v>
+      </c>
+      <c r="C296" t="s">
+        <v>414</v>
       </c>
       <c r="D296" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="E296" t="s">
-        <v>408</v>
+        <v>17</v>
       </c>
       <c r="F296" t="s">
-        <v>408</v>
+        <v>17</v>
       </c>
       <c r="G296" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="H296" t="s">
         <v>403</v>
       </c>
+      <c r="J296">
+        <v>2019</v>
+      </c>
+      <c r="K296">
+        <v>2018</v>
+      </c>
       <c r="M296" t="s">
         <v>229</v>
       </c>
@@ -13511,22 +13536,19 @@
     </row>
     <row r="297" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="B297" t="s">
-        <v>433</v>
-      </c>
-      <c r="C297" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="D297" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="E297" t="s">
         <v>408</v>
       </c>
       <c r="F297" t="s">
-        <v>435</v>
+        <v>408</v>
       </c>
       <c r="G297" t="s">
         <v>17</v>
@@ -13543,19 +13565,22 @@
     </row>
     <row r="298" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
-        <v>436</v>
+        <v>432</v>
       </c>
       <c r="B298" t="s">
-        <v>437</v>
+        <v>433</v>
+      </c>
+      <c r="C298" t="s">
+        <v>434</v>
       </c>
       <c r="D298" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="E298" t="s">
         <v>408</v>
       </c>
       <c r="F298" t="s">
-        <v>408</v>
+        <v>435</v>
       </c>
       <c r="G298" t="s">
         <v>17</v>
@@ -13572,10 +13597,10 @@
     </row>
     <row r="299" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="B299" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="D299" t="s">
         <v>17</v>
@@ -13601,10 +13626,10 @@
     </row>
     <row r="300" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="B300" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="D300" t="s">
         <v>17</v>
@@ -13630,10 +13655,10 @@
     </row>
     <row r="301" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="B301" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="D301" t="s">
         <v>17</v>
@@ -13642,17 +13667,14 @@
         <v>408</v>
       </c>
       <c r="F301" t="s">
-        <v>17</v>
+        <v>408</v>
       </c>
       <c r="G301" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="H301" t="s">
         <v>403</v>
       </c>
-      <c r="K301">
-        <v>2019</v>
-      </c>
       <c r="M301" t="s">
         <v>229</v>
       </c>
@@ -13662,16 +13684,16 @@
     </row>
     <row r="302" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="B302" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="D302" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="E302" t="s">
-        <v>17</v>
+        <v>408</v>
       </c>
       <c r="F302" t="s">
         <v>17</v>
@@ -13682,11 +13704,8 @@
       <c r="H302" t="s">
         <v>403</v>
       </c>
-      <c r="J302">
+      <c r="K302">
         <v>2019</v>
-      </c>
-      <c r="K302">
-        <v>1990</v>
       </c>
       <c r="M302" t="s">
         <v>229</v>
@@ -13697,10 +13716,10 @@
     </row>
     <row r="303" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A303" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="B303" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="D303" t="s">
         <v>29</v>
@@ -13732,10 +13751,10 @@
     </row>
     <row r="304" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A304" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="B304" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="D304" t="s">
         <v>29</v>
@@ -13767,29 +13786,32 @@
     </row>
     <row r="305" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A305" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="B305" t="s">
-        <v>451</v>
-      </c>
-      <c r="C305" t="s">
-        <v>597</v>
+        <v>449</v>
       </c>
       <c r="D305" t="s">
         <v>29</v>
       </c>
       <c r="E305" t="s">
-        <v>452</v>
+        <v>17</v>
       </c>
       <c r="F305" t="s">
         <v>17</v>
       </c>
       <c r="G305" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="H305" t="s">
         <v>403</v>
       </c>
+      <c r="J305">
+        <v>2019</v>
+      </c>
+      <c r="K305">
+        <v>1990</v>
+      </c>
       <c r="M305" t="s">
         <v>229</v>
       </c>
@@ -13799,29 +13821,29 @@
     </row>
     <row r="306" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A306" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="B306" t="s">
-        <v>454</v>
+        <v>451</v>
+      </c>
+      <c r="C306" t="s">
+        <v>597</v>
       </c>
       <c r="D306" t="s">
         <v>29</v>
       </c>
       <c r="E306" t="s">
-        <v>17</v>
+        <v>452</v>
       </c>
       <c r="F306" t="s">
         <v>17</v>
       </c>
       <c r="G306" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="H306" t="s">
         <v>403</v>
       </c>
-      <c r="K306">
-        <v>2019</v>
-      </c>
       <c r="M306" t="s">
         <v>229</v>
       </c>
@@ -13831,10 +13853,10 @@
     </row>
     <row r="307" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A307" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="B307" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="D307" t="s">
         <v>29</v>
@@ -13851,11 +13873,8 @@
       <c r="H307" t="s">
         <v>403</v>
       </c>
-      <c r="J307">
+      <c r="K307">
         <v>2019</v>
-      </c>
-      <c r="K307">
-        <v>1990</v>
       </c>
       <c r="M307" t="s">
         <v>229</v>
@@ -13866,26 +13885,32 @@
     </row>
     <row r="308" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A308" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="B308" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="D308" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="E308" t="s">
-        <v>408</v>
+        <v>17</v>
       </c>
       <c r="F308" t="s">
-        <v>199</v>
+        <v>17</v>
       </c>
       <c r="G308" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="H308" t="s">
         <v>403</v>
       </c>
+      <c r="J308">
+        <v>2019</v>
+      </c>
+      <c r="K308">
+        <v>1990</v>
+      </c>
       <c r="M308" t="s">
         <v>229</v>
       </c>
@@ -13895,29 +13920,26 @@
     </row>
     <row r="309" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A309" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="B309" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="D309" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="E309" t="s">
-        <v>17</v>
+        <v>408</v>
       </c>
       <c r="F309" t="s">
-        <v>17</v>
+        <v>199</v>
       </c>
       <c r="G309" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="H309" t="s">
         <v>403</v>
       </c>
-      <c r="K309">
-        <v>2019</v>
-      </c>
       <c r="M309" t="s">
         <v>229</v>
       </c>
@@ -13927,19 +13949,16 @@
     </row>
     <row r="310" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A310" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="B310" t="s">
-        <v>462</v>
-      </c>
-      <c r="C310" t="s">
-        <v>598</v>
+        <v>460</v>
       </c>
       <c r="D310" t="s">
         <v>29</v>
       </c>
       <c r="E310" t="s">
-        <v>408</v>
+        <v>17</v>
       </c>
       <c r="F310" t="s">
         <v>17</v>
@@ -13951,7 +13970,7 @@
         <v>403</v>
       </c>
       <c r="K310">
-        <v>2001</v>
+        <v>2019</v>
       </c>
       <c r="M310" t="s">
         <v>229</v>
@@ -13962,10 +13981,10 @@
     </row>
     <row r="311" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A311" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="B311" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="C311" t="s">
         <v>598</v>
@@ -13997,10 +14016,10 @@
     </row>
     <row r="312" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A312" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="B312" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="C312" t="s">
         <v>598</v>
@@ -14032,10 +14051,10 @@
     </row>
     <row r="313" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A313" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="B313" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="C313" t="s">
         <v>598</v>
@@ -14067,10 +14086,10 @@
     </row>
     <row r="314" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A314" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="B314" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="C314" t="s">
         <v>598</v>
@@ -14102,10 +14121,10 @@
     </row>
     <row r="315" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A315" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="B315" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="C315" t="s">
         <v>598</v>
@@ -14137,13 +14156,13 @@
     </row>
     <row r="316" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A316" t="s">
-        <v>478</v>
+        <v>471</v>
       </c>
       <c r="B316" t="s">
-        <v>599</v>
+        <v>472</v>
       </c>
       <c r="C316" t="s">
-        <v>604</v>
+        <v>598</v>
       </c>
       <c r="D316" t="s">
         <v>29</v>
@@ -14172,10 +14191,10 @@
     </row>
     <row r="317" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A317" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="B317" t="s">
-        <v>480</v>
+        <v>599</v>
       </c>
       <c r="C317" t="s">
         <v>604</v>
@@ -14207,19 +14226,19 @@
     </row>
     <row r="318" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A318" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="B318" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="C318" t="s">
-        <v>159</v>
+        <v>604</v>
       </c>
       <c r="D318" t="s">
         <v>29</v>
       </c>
       <c r="E318" t="s">
-        <v>452</v>
+        <v>408</v>
       </c>
       <c r="F318" t="s">
         <v>17</v>
@@ -14242,10 +14261,10 @@
     </row>
     <row r="319" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A319" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="B319" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="C319" t="s">
         <v>159</v>
@@ -14254,7 +14273,7 @@
         <v>29</v>
       </c>
       <c r="E319" t="s">
-        <v>408</v>
+        <v>452</v>
       </c>
       <c r="F319" t="s">
         <v>17</v>
@@ -14277,13 +14296,13 @@
     </row>
     <row r="320" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A320" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="B320" t="s">
-        <v>606</v>
+        <v>484</v>
       </c>
       <c r="C320" t="s">
-        <v>600</v>
+        <v>159</v>
       </c>
       <c r="D320" t="s">
         <v>29</v>
@@ -14312,10 +14331,10 @@
     </row>
     <row r="321" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A321" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="B321" t="s">
-        <v>603</v>
+        <v>606</v>
       </c>
       <c r="C321" t="s">
         <v>600</v>
@@ -14347,13 +14366,13 @@
     </row>
     <row r="322" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A322" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B322" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="C322" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="D322" t="s">
         <v>29</v>
@@ -14382,19 +14401,19 @@
     </row>
     <row r="323" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A323" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="B323" t="s">
-        <v>489</v>
+        <v>607</v>
       </c>
       <c r="C323" t="s">
-        <v>6</v>
+        <v>602</v>
       </c>
       <c r="D323" t="s">
         <v>29</v>
       </c>
       <c r="E323" t="s">
-        <v>17</v>
+        <v>408</v>
       </c>
       <c r="F323" t="s">
         <v>17</v>
@@ -14417,10 +14436,10 @@
     </row>
     <row r="324" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A324" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="B324" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="C324" t="s">
         <v>6</v>
@@ -14429,7 +14448,7 @@
         <v>29</v>
       </c>
       <c r="E324" t="s">
-        <v>199</v>
+        <v>17</v>
       </c>
       <c r="F324" t="s">
         <v>17</v>
@@ -14452,19 +14471,19 @@
     </row>
     <row r="325" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A325" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="B325" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="C325" t="s">
-        <v>601</v>
+        <v>6</v>
       </c>
       <c r="D325" t="s">
         <v>29</v>
       </c>
       <c r="E325" t="s">
-        <v>408</v>
+        <v>199</v>
       </c>
       <c r="F325" t="s">
         <v>17</v>
@@ -14487,16 +14506,16 @@
     </row>
     <row r="326" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A326" t="s">
-        <v>591</v>
+        <v>492</v>
       </c>
       <c r="B326" t="s">
-        <v>592</v>
+        <v>493</v>
       </c>
       <c r="C326" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
       <c r="D326" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="E326" t="s">
         <v>408</v>
@@ -14522,16 +14541,16 @@
     </row>
     <row r="327" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A327" t="s">
-        <v>605</v>
+        <v>591</v>
       </c>
       <c r="B327" t="s">
-        <v>609</v>
+        <v>592</v>
       </c>
       <c r="C327" t="s">
-        <v>598</v>
+        <v>604</v>
       </c>
       <c r="D327" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="E327" t="s">
         <v>408</v>
@@ -14557,54 +14576,60 @@
     </row>
     <row r="328" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A328" t="s">
-        <v>706</v>
+        <v>605</v>
       </c>
       <c r="B328" t="s">
-        <v>705</v>
+        <v>609</v>
+      </c>
+      <c r="C328" t="s">
+        <v>598</v>
       </c>
       <c r="D328" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="E328" t="s">
-        <v>17</v>
+        <v>408</v>
       </c>
       <c r="F328" t="s">
         <v>17</v>
       </c>
       <c r="G328" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="H328" t="s">
-        <v>36</v>
+        <v>403</v>
       </c>
       <c r="K328">
-        <v>2000</v>
+        <v>2001</v>
+      </c>
+      <c r="M328" t="s">
+        <v>229</v>
+      </c>
+      <c r="N328" t="s">
+        <v>229</v>
       </c>
     </row>
     <row r="329" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A329" t="s">
-        <v>713</v>
+        <v>706</v>
       </c>
       <c r="B329" t="s">
-        <v>728</v>
-      </c>
-      <c r="C329" t="s">
-        <v>6</v>
+        <v>705</v>
       </c>
       <c r="D329" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="E329" t="s">
-        <v>199</v>
+        <v>17</v>
       </c>
       <c r="F329" t="s">
         <v>17</v>
       </c>
       <c r="G329" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="H329" t="s">
-        <v>277</v>
+        <v>36</v>
       </c>
       <c r="K329">
         <v>2000</v>
@@ -14612,10 +14637,10 @@
     </row>
     <row r="330" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A330" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="B330" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="C330" t="s">
         <v>6</v>
@@ -14633,7 +14658,7 @@
         <v>8</v>
       </c>
       <c r="H330" t="s">
-        <v>520</v>
+        <v>277</v>
       </c>
       <c r="K330">
         <v>2000</v>
@@ -14641,10 +14666,10 @@
     </row>
     <row r="331" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A331" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="B331" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="C331" t="s">
         <v>6</v>
@@ -14662,7 +14687,7 @@
         <v>8</v>
       </c>
       <c r="H331" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="K331">
         <v>2000</v>
@@ -14670,10 +14695,10 @@
     </row>
     <row r="332" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A332" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="B332" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="C332" t="s">
         <v>6</v>
@@ -14691,7 +14716,7 @@
         <v>8</v>
       </c>
       <c r="H332" t="s">
-        <v>548</v>
+        <v>521</v>
       </c>
       <c r="K332">
         <v>2000</v>
@@ -14699,10 +14724,10 @@
     </row>
     <row r="333" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A333" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="B333" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="C333" t="s">
         <v>6</v>
@@ -14720,7 +14745,7 @@
         <v>8</v>
       </c>
       <c r="H333" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="K333">
         <v>2000</v>
@@ -14728,33 +14753,39 @@
     </row>
     <row r="334" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A334" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="B334" t="s">
-        <v>723</v>
+        <v>732</v>
+      </c>
+      <c r="C334" t="s">
+        <v>6</v>
       </c>
       <c r="D334" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="E334" t="s">
         <v>199</v>
       </c>
       <c r="F334" t="s">
-        <v>275</v>
+        <v>17</v>
       </c>
       <c r="G334" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="H334" t="s">
-        <v>277</v>
+        <v>549</v>
+      </c>
+      <c r="K334">
+        <v>2000</v>
       </c>
     </row>
     <row r="335" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A335" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="B335" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="D335" t="s">
         <v>17</v>
@@ -14769,15 +14800,15 @@
         <v>17</v>
       </c>
       <c r="H335" t="s">
-        <v>520</v>
+        <v>277</v>
       </c>
     </row>
     <row r="336" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A336" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="B336" t="s">
-        <v>726</v>
+        <v>724</v>
       </c>
       <c r="D336" t="s">
         <v>17</v>
@@ -14792,15 +14823,15 @@
         <v>17</v>
       </c>
       <c r="H336" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
     </row>
     <row r="337" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A337" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="B337" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="D337" t="s">
         <v>17</v>
@@ -14815,15 +14846,15 @@
         <v>17</v>
       </c>
       <c r="H337" t="s">
-        <v>548</v>
+        <v>521</v>
       </c>
     </row>
     <row r="338" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A338" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="B338" t="s">
-        <v>727</v>
+        <v>725</v>
       </c>
       <c r="D338" t="s">
         <v>17</v>
@@ -14838,53 +14869,47 @@
         <v>17</v>
       </c>
       <c r="H338" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
     </row>
     <row r="339" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A339" t="s">
-        <v>733</v>
+        <v>722</v>
       </c>
       <c r="B339" t="s">
-        <v>734</v>
-      </c>
-      <c r="C339" t="s">
-        <v>735</v>
+        <v>727</v>
       </c>
       <c r="D339" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="E339" t="s">
-        <v>311</v>
+        <v>199</v>
       </c>
       <c r="F339" t="s">
-        <v>17</v>
+        <v>275</v>
       </c>
       <c r="G339" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="H339" t="s">
-        <v>313</v>
-      </c>
-      <c r="K339">
-        <v>2014</v>
+        <v>549</v>
       </c>
     </row>
     <row r="340" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A340" t="s">
-        <v>736</v>
+        <v>733</v>
       </c>
       <c r="B340" t="s">
-        <v>737</v>
+        <v>734</v>
       </c>
       <c r="C340" t="s">
-        <v>260</v>
+        <v>735</v>
       </c>
       <c r="D340" t="s">
         <v>29</v>
       </c>
       <c r="E340" t="s">
-        <v>17</v>
+        <v>311</v>
       </c>
       <c r="F340" t="s">
         <v>17</v>
@@ -14895,211 +14920,186 @@
       <c r="H340" t="s">
         <v>313</v>
       </c>
-      <c r="I340" t="s">
-        <v>9</v>
-      </c>
-      <c r="J340" t="s">
-        <v>9</v>
-      </c>
       <c r="K340">
+        <v>2014</v>
+      </c>
+    </row>
+    <row r="341" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A341" t="s">
+        <v>736</v>
+      </c>
+      <c r="B341" t="s">
+        <v>737</v>
+      </c>
+      <c r="C341" t="s">
+        <v>260</v>
+      </c>
+      <c r="D341" t="s">
+        <v>29</v>
+      </c>
+      <c r="E341" t="s">
+        <v>17</v>
+      </c>
+      <c r="F341" t="s">
+        <v>17</v>
+      </c>
+      <c r="G341" t="s">
+        <v>8</v>
+      </c>
+      <c r="H341" t="s">
+        <v>313</v>
+      </c>
+      <c r="I341" t="s">
+        <v>9</v>
+      </c>
+      <c r="J341" t="s">
+        <v>9</v>
+      </c>
+      <c r="K341">
         <v>2001</v>
       </c>
-      <c r="L340" t="s">
-        <v>9</v>
-      </c>
-      <c r="N340" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="341" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A341" s="2" t="s">
-        <v>792</v>
-      </c>
-      <c r="B341" s="2" t="s">
-        <v>793</v>
-      </c>
-      <c r="C341" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="D341" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="E341" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="F341" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="G341" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="H341" s="2" t="s">
-        <v>313</v>
-      </c>
-      <c r="I341" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="J341" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="K341" s="2"/>
-      <c r="L341" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="M341" s="2"/>
-      <c r="N341" s="2" t="s">
+      <c r="L341" t="s">
+        <v>9</v>
+      </c>
+      <c r="N341" t="s">
         <v>229</v>
       </c>
     </row>
     <row r="342" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A342" s="2" t="s">
+        <v>807</v>
+      </c>
+      <c r="B342" s="2" t="s">
+        <v>808</v>
+      </c>
+      <c r="C342" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="D342" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E342" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F342" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G342" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H342" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="I342" s="2"/>
+      <c r="J342" s="2"/>
+      <c r="K342" s="2">
+        <v>2001</v>
+      </c>
+      <c r="L342" s="2"/>
+      <c r="M342" s="2"/>
+      <c r="N342" s="2"/>
+    </row>
+    <row r="343" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A343" s="2" t="s">
+        <v>792</v>
+      </c>
+      <c r="B343" s="2" t="s">
+        <v>793</v>
+      </c>
+      <c r="C343" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D343" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E343" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="F343" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G343" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H343" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="I343" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="J343" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="K343" s="2"/>
+      <c r="L343" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="M343" s="2"/>
+      <c r="N343" s="2" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="344" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A344" s="2" t="s">
         <v>794</v>
       </c>
-      <c r="B342" s="2" t="s">
+      <c r="B344" s="2" t="s">
         <v>793</v>
       </c>
-      <c r="C342" s="2" t="s">
+      <c r="C344" s="2" t="s">
         <v>795</v>
       </c>
-      <c r="D342" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="E342" s="2" t="s">
+      <c r="D344" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E344" s="2" t="s">
         <v>199</v>
       </c>
-      <c r="F342" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="G342" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="H342" s="2" t="s">
+      <c r="F344" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G344" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H344" s="2" t="s">
         <v>313</v>
       </c>
-      <c r="I342" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="J342" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="K342" s="2"/>
-      <c r="L342" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="M342" s="2"/>
-      <c r="N342" s="2" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="343" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A343" t="s">
-        <v>168</v>
-      </c>
-      <c r="B343" t="s">
-        <v>169</v>
-      </c>
-      <c r="C343" t="s">
-        <v>187</v>
-      </c>
-      <c r="D343" t="s">
-        <v>29</v>
-      </c>
-      <c r="E343" t="s">
-        <v>197</v>
-      </c>
-      <c r="F343" t="s">
-        <v>198</v>
-      </c>
-      <c r="G343" t="s">
-        <v>17</v>
-      </c>
-      <c r="H343" t="s">
-        <v>31</v>
-      </c>
-      <c r="I343" t="s">
-        <v>9</v>
-      </c>
-      <c r="J343" t="s">
-        <v>9</v>
-      </c>
-      <c r="K343">
-        <v>2001</v>
-      </c>
-      <c r="L343" t="s">
-        <v>9</v>
-      </c>
-      <c r="M343" t="s">
-        <v>229</v>
-      </c>
-      <c r="N343" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="344" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A344" t="s">
-        <v>96</v>
-      </c>
-      <c r="B344" t="s">
-        <v>125</v>
-      </c>
-      <c r="C344" t="s">
-        <v>159</v>
-      </c>
-      <c r="D344" t="s">
-        <v>29</v>
-      </c>
-      <c r="E344" t="s">
-        <v>17</v>
-      </c>
-      <c r="F344" t="s">
-        <v>17</v>
-      </c>
-      <c r="G344" t="s">
-        <v>8</v>
-      </c>
-      <c r="H344" t="s">
-        <v>31</v>
-      </c>
-      <c r="I344" t="s">
-        <v>9</v>
-      </c>
-      <c r="J344" t="s">
-        <v>9</v>
-      </c>
-      <c r="K344">
-        <v>2001</v>
-      </c>
-      <c r="L344" t="s">
-        <v>9</v>
-      </c>
-      <c r="M344" t="s">
-        <v>229</v>
-      </c>
-      <c r="N344" t="s">
+      <c r="I344" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="J344" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="K344" s="2"/>
+      <c r="L344" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="M344" s="2"/>
+      <c r="N344" s="2" t="s">
         <v>229</v>
       </c>
     </row>
     <row r="345" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A345" t="s">
-        <v>254</v>
+        <v>168</v>
       </c>
       <c r="B345" t="s">
-        <v>255</v>
+        <v>169</v>
       </c>
       <c r="C345" t="s">
-        <v>253</v>
+        <v>187</v>
       </c>
       <c r="D345" t="s">
         <v>29</v>
       </c>
       <c r="E345" t="s">
-        <v>17</v>
+        <v>197</v>
       </c>
       <c r="F345" t="s">
-        <v>17</v>
+        <v>198</v>
       </c>
       <c r="G345" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="H345" t="s">
         <v>31</v>
@@ -15125,19 +15125,19 @@
     </row>
     <row r="346" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A346" t="s">
-        <v>264</v>
+        <v>96</v>
       </c>
       <c r="B346" t="s">
-        <v>270</v>
+        <v>125</v>
       </c>
       <c r="C346" t="s">
-        <v>265</v>
+        <v>159</v>
       </c>
       <c r="D346" t="s">
         <v>29</v>
       </c>
       <c r="E346" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="F346" t="s">
         <v>17</v>
@@ -15155,10 +15155,10 @@
         <v>9</v>
       </c>
       <c r="K346">
-        <v>2010</v>
+        <v>2001</v>
       </c>
       <c r="L346" t="s">
-        <v>224</v>
+        <v>9</v>
       </c>
       <c r="M346" t="s">
         <v>229</v>
@@ -15169,19 +15169,19 @@
     </row>
     <row r="347" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A347" t="s">
-        <v>70</v>
+        <v>254</v>
       </c>
       <c r="B347" t="s">
-        <v>173</v>
+        <v>255</v>
       </c>
       <c r="C347" t="s">
-        <v>188</v>
+        <v>253</v>
       </c>
       <c r="D347" t="s">
         <v>29</v>
       </c>
       <c r="E347" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="F347" t="s">
         <v>17</v>
@@ -15213,13 +15213,13 @@
     </row>
     <row r="348" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A348" t="s">
-        <v>744</v>
+        <v>264</v>
       </c>
       <c r="B348" t="s">
-        <v>745</v>
+        <v>270</v>
       </c>
       <c r="C348" t="s">
-        <v>253</v>
+        <v>265</v>
       </c>
       <c r="D348" t="s">
         <v>29</v>
@@ -15236,8 +15236,17 @@
       <c r="H348" t="s">
         <v>31</v>
       </c>
+      <c r="I348" t="s">
+        <v>9</v>
+      </c>
+      <c r="J348" t="s">
+        <v>9</v>
+      </c>
       <c r="K348">
-        <v>2001</v>
+        <v>2010</v>
+      </c>
+      <c r="L348" t="s">
+        <v>224</v>
       </c>
       <c r="M348" t="s">
         <v>229</v>
@@ -15248,13 +15257,13 @@
     </row>
     <row r="349" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A349" t="s">
-        <v>742</v>
+        <v>70</v>
       </c>
       <c r="B349" t="s">
-        <v>743</v>
+        <v>173</v>
       </c>
       <c r="C349" t="s">
-        <v>253</v>
+        <v>188</v>
       </c>
       <c r="D349" t="s">
         <v>29</v>
@@ -15271,9 +15280,18 @@
       <c r="H349" t="s">
         <v>31</v>
       </c>
+      <c r="I349" t="s">
+        <v>9</v>
+      </c>
+      <c r="J349" t="s">
+        <v>9</v>
+      </c>
       <c r="K349">
         <v>2001</v>
       </c>
+      <c r="L349" t="s">
+        <v>9</v>
+      </c>
       <c r="M349" t="s">
         <v>229</v>
       </c>
@@ -15283,13 +15301,13 @@
     </row>
     <row r="350" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A350" t="s">
-        <v>69</v>
+        <v>744</v>
       </c>
       <c r="B350" t="s">
-        <v>172</v>
+        <v>745</v>
       </c>
       <c r="C350" t="s">
-        <v>188</v>
+        <v>253</v>
       </c>
       <c r="D350" t="s">
         <v>29</v>
@@ -15306,18 +15324,9 @@
       <c r="H350" t="s">
         <v>31</v>
       </c>
-      <c r="I350" t="s">
-        <v>9</v>
-      </c>
-      <c r="J350" t="s">
-        <v>9</v>
-      </c>
       <c r="K350">
         <v>2001</v>
       </c>
-      <c r="L350" t="s">
-        <v>9</v>
-      </c>
       <c r="M350" t="s">
         <v>229</v>
       </c>
@@ -15327,41 +15336,32 @@
     </row>
     <row r="351" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A351" t="s">
-        <v>75</v>
+        <v>742</v>
       </c>
       <c r="B351" t="s">
-        <v>178</v>
+        <v>743</v>
       </c>
       <c r="C351" t="s">
-        <v>187</v>
+        <v>253</v>
       </c>
       <c r="D351" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="E351" t="s">
         <v>11</v>
       </c>
       <c r="F351" t="s">
-        <v>199</v>
+        <v>17</v>
       </c>
       <c r="G351" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="H351" t="s">
         <v>31</v>
       </c>
-      <c r="I351" t="s">
-        <v>9</v>
-      </c>
-      <c r="J351" t="s">
-        <v>9</v>
-      </c>
       <c r="K351">
         <v>2001</v>
       </c>
-      <c r="L351" t="s">
-        <v>9</v>
-      </c>
       <c r="M351" t="s">
         <v>229</v>
       </c>
@@ -15371,19 +15371,19 @@
     </row>
     <row r="352" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A352" t="s">
-        <v>251</v>
+        <v>69</v>
       </c>
       <c r="B352" t="s">
-        <v>252</v>
+        <v>172</v>
       </c>
       <c r="C352" t="s">
-        <v>253</v>
+        <v>188</v>
       </c>
       <c r="D352" t="s">
         <v>29</v>
       </c>
       <c r="E352" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F352" t="s">
         <v>17</v>
@@ -15415,25 +15415,25 @@
     </row>
     <row r="353" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A353" t="s">
-        <v>235</v>
+        <v>75</v>
       </c>
       <c r="B353" t="s">
-        <v>246</v>
+        <v>178</v>
       </c>
       <c r="C353" t="s">
-        <v>6</v>
+        <v>187</v>
       </c>
       <c r="D353" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="E353" t="s">
-        <v>41</v>
+        <v>11</v>
       </c>
       <c r="F353" t="s">
-        <v>17</v>
+        <v>199</v>
       </c>
       <c r="G353" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="H353" t="s">
         <v>31</v>
@@ -15445,10 +15445,10 @@
         <v>9</v>
       </c>
       <c r="K353">
-        <v>2010</v>
+        <v>2001</v>
       </c>
       <c r="L353" t="s">
-        <v>224</v>
+        <v>9</v>
       </c>
       <c r="M353" t="s">
         <v>229</v>
@@ -15459,13 +15459,13 @@
     </row>
     <row r="354" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A354" t="s">
-        <v>266</v>
+        <v>251</v>
       </c>
       <c r="B354" t="s">
-        <v>269</v>
+        <v>252</v>
       </c>
       <c r="C354" t="s">
-        <v>260</v>
+        <v>253</v>
       </c>
       <c r="D354" t="s">
         <v>29</v>
@@ -15489,10 +15489,10 @@
         <v>9</v>
       </c>
       <c r="K354">
-        <v>2010</v>
+        <v>2001</v>
       </c>
       <c r="L354" t="s">
-        <v>224</v>
+        <v>9</v>
       </c>
       <c r="M354" t="s">
         <v>229</v>
@@ -15503,19 +15503,19 @@
     </row>
     <row r="355" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A355" t="s">
-        <v>258</v>
+        <v>235</v>
       </c>
       <c r="B355" t="s">
-        <v>263</v>
+        <v>246</v>
       </c>
       <c r="C355" t="s">
-        <v>260</v>
+        <v>6</v>
       </c>
       <c r="D355" t="s">
         <v>29</v>
       </c>
       <c r="E355" t="s">
-        <v>17</v>
+        <v>41</v>
       </c>
       <c r="F355" t="s">
         <v>17</v>
@@ -15533,10 +15533,13 @@
         <v>9</v>
       </c>
       <c r="K355">
-        <v>2001</v>
+        <v>2010</v>
       </c>
       <c r="L355" t="s">
-        <v>9</v>
+        <v>224</v>
+      </c>
+      <c r="M355" t="s">
+        <v>229</v>
       </c>
       <c r="N355" t="s">
         <v>229</v>
@@ -15544,25 +15547,25 @@
     </row>
     <row r="356" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A356" t="s">
-        <v>207</v>
+        <v>266</v>
       </c>
       <c r="B356" t="s">
-        <v>208</v>
+        <v>269</v>
       </c>
       <c r="C356" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D356" t="s">
         <v>29</v>
       </c>
       <c r="E356" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="F356" t="s">
-        <v>209</v>
+        <v>17</v>
       </c>
       <c r="G356" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="H356" t="s">
         <v>31</v>
@@ -15574,10 +15577,10 @@
         <v>9</v>
       </c>
       <c r="K356">
-        <v>2001</v>
+        <v>2010</v>
       </c>
       <c r="L356" t="s">
-        <v>9</v>
+        <v>224</v>
       </c>
       <c r="M356" t="s">
         <v>229</v>
@@ -15588,19 +15591,19 @@
     </row>
     <row r="357" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A357" t="s">
-        <v>767</v>
+        <v>258</v>
       </c>
       <c r="B357" t="s">
-        <v>772</v>
+        <v>263</v>
       </c>
       <c r="C357" t="s">
-        <v>777</v>
+        <v>260</v>
       </c>
       <c r="D357" t="s">
         <v>29</v>
       </c>
       <c r="E357" t="s">
-        <v>275</v>
+        <v>17</v>
       </c>
       <c r="F357" t="s">
         <v>17</v>
@@ -15609,7 +15612,7 @@
         <v>8</v>
       </c>
       <c r="H357" t="s">
-        <v>277</v>
+        <v>31</v>
       </c>
       <c r="I357" t="s">
         <v>9</v>
@@ -15618,13 +15621,10 @@
         <v>9</v>
       </c>
       <c r="K357">
-        <v>2000</v>
+        <v>2001</v>
       </c>
       <c r="L357" t="s">
         <v>9</v>
-      </c>
-      <c r="M357" t="s">
-        <v>229</v>
       </c>
       <c r="N357" t="s">
         <v>229</v>
@@ -15632,28 +15632,28 @@
     </row>
     <row r="358" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A358" t="s">
-        <v>768</v>
+        <v>207</v>
       </c>
       <c r="B358" t="s">
-        <v>773</v>
+        <v>208</v>
       </c>
       <c r="C358" t="s">
-        <v>777</v>
+        <v>259</v>
       </c>
       <c r="D358" t="s">
         <v>29</v>
       </c>
       <c r="E358" t="s">
-        <v>275</v>
+        <v>11</v>
       </c>
       <c r="F358" t="s">
-        <v>17</v>
+        <v>209</v>
       </c>
       <c r="G358" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="H358" t="s">
-        <v>520</v>
+        <v>31</v>
       </c>
       <c r="I358" t="s">
         <v>9</v>
@@ -15662,7 +15662,7 @@
         <v>9</v>
       </c>
       <c r="K358">
-        <v>2000</v>
+        <v>2001</v>
       </c>
       <c r="L358" t="s">
         <v>9</v>
@@ -15676,10 +15676,10 @@
     </row>
     <row r="359" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A359" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="B359" t="s">
-        <v>774</v>
+        <v>772</v>
       </c>
       <c r="C359" t="s">
         <v>777</v>
@@ -15697,7 +15697,7 @@
         <v>8</v>
       </c>
       <c r="H359" t="s">
-        <v>521</v>
+        <v>277</v>
       </c>
       <c r="I359" t="s">
         <v>9</v>
@@ -15720,10 +15720,10 @@
     </row>
     <row r="360" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A360" t="s">
-        <v>770</v>
+        <v>768</v>
       </c>
       <c r="B360" t="s">
-        <v>775</v>
+        <v>773</v>
       </c>
       <c r="C360" t="s">
         <v>777</v>
@@ -15741,7 +15741,7 @@
         <v>8</v>
       </c>
       <c r="H360" t="s">
-        <v>548</v>
+        <v>520</v>
       </c>
       <c r="I360" t="s">
         <v>9</v>
@@ -15764,10 +15764,10 @@
     </row>
     <row r="361" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A361" t="s">
-        <v>771</v>
+        <v>769</v>
       </c>
       <c r="B361" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
       <c r="C361" t="s">
         <v>777</v>
@@ -15785,7 +15785,7 @@
         <v>8</v>
       </c>
       <c r="H361" t="s">
-        <v>549</v>
+        <v>521</v>
       </c>
       <c r="I361" t="s">
         <v>9</v>
@@ -15808,19 +15808,19 @@
     </row>
     <row r="362" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A362" t="s">
-        <v>778</v>
+        <v>770</v>
       </c>
       <c r="B362" t="s">
-        <v>203</v>
+        <v>775</v>
       </c>
       <c r="C362" t="s">
-        <v>187</v>
+        <v>777</v>
       </c>
       <c r="D362" t="s">
         <v>29</v>
       </c>
       <c r="E362" t="s">
-        <v>11</v>
+        <v>275</v>
       </c>
       <c r="F362" t="s">
         <v>17</v>
@@ -15829,7 +15829,7 @@
         <v>8</v>
       </c>
       <c r="H362" t="s">
-        <v>31</v>
+        <v>548</v>
       </c>
       <c r="I362" t="s">
         <v>9</v>
@@ -15838,10 +15838,13 @@
         <v>9</v>
       </c>
       <c r="K362">
-        <v>2010</v>
+        <v>2000</v>
       </c>
       <c r="L362" t="s">
-        <v>224</v>
+        <v>9</v>
+      </c>
+      <c r="M362" t="s">
+        <v>229</v>
       </c>
       <c r="N362" t="s">
         <v>229</v>
@@ -15849,19 +15852,19 @@
     </row>
     <row r="363" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A363" t="s">
-        <v>779</v>
+        <v>771</v>
       </c>
       <c r="B363" t="s">
-        <v>142</v>
+        <v>776</v>
       </c>
       <c r="C363" t="s">
-        <v>188</v>
+        <v>777</v>
       </c>
       <c r="D363" t="s">
         <v>29</v>
       </c>
       <c r="E363" t="s">
-        <v>11</v>
+        <v>275</v>
       </c>
       <c r="F363" t="s">
         <v>17</v>
@@ -15870,7 +15873,7 @@
         <v>8</v>
       </c>
       <c r="H363" t="s">
-        <v>31</v>
+        <v>549</v>
       </c>
       <c r="I363" t="s">
         <v>9</v>
@@ -15879,10 +15882,13 @@
         <v>9</v>
       </c>
       <c r="K363">
-        <v>2010</v>
+        <v>2000</v>
       </c>
       <c r="L363" t="s">
-        <v>224</v>
+        <v>9</v>
+      </c>
+      <c r="M363" t="s">
+        <v>229</v>
       </c>
       <c r="N363" t="s">
         <v>229</v>
@@ -15890,13 +15896,13 @@
     </row>
     <row r="364" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A364" t="s">
-        <v>780</v>
+        <v>778</v>
       </c>
       <c r="B364" t="s">
-        <v>141</v>
+        <v>203</v>
       </c>
       <c r="C364" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D364" t="s">
         <v>29</v>
@@ -15929,12 +15935,12 @@
         <v>229</v>
       </c>
     </row>
-    <row r="365" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A365" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
       <c r="B365" t="s">
-        <v>152</v>
+        <v>142</v>
       </c>
       <c r="C365" t="s">
         <v>188</v>
@@ -15972,10 +15978,10 @@
     </row>
     <row r="366" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A366" t="s">
-        <v>782</v>
+        <v>780</v>
       </c>
       <c r="B366" t="s">
-        <v>172</v>
+        <v>141</v>
       </c>
       <c r="C366" t="s">
         <v>188</v>
@@ -16005,27 +16011,27 @@
         <v>2010</v>
       </c>
       <c r="L366" t="s">
-        <v>9</v>
-      </c>
-      <c r="M366" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="N366" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="367" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A367" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="B367" t="s">
-        <v>785</v>
+        <v>152</v>
+      </c>
+      <c r="C367" t="s">
+        <v>188</v>
       </c>
       <c r="D367" t="s">
         <v>29</v>
       </c>
       <c r="E367" t="s">
-        <v>408</v>
+        <v>11</v>
       </c>
       <c r="F367" t="s">
         <v>17</v>
@@ -16034,7 +16040,7 @@
         <v>8</v>
       </c>
       <c r="H367" t="s">
-        <v>403</v>
+        <v>31</v>
       </c>
       <c r="I367" t="s">
         <v>9</v>
@@ -16043,13 +16049,10 @@
         <v>9</v>
       </c>
       <c r="K367">
-        <v>2001</v>
+        <v>2010</v>
       </c>
       <c r="L367" t="s">
-        <v>9</v>
-      </c>
-      <c r="M367" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="N367" t="s">
         <v>229</v>
@@ -16057,10 +16060,13 @@
     </row>
     <row r="368" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A368" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
       <c r="B368" t="s">
-        <v>786</v>
+        <v>172</v>
+      </c>
+      <c r="C368" t="s">
+        <v>188</v>
       </c>
       <c r="D368" t="s">
         <v>29</v>
@@ -16084,11 +16090,93 @@
         <v>9</v>
       </c>
       <c r="K368">
+        <v>2010</v>
+      </c>
+      <c r="L368" t="s">
+        <v>9</v>
+      </c>
+      <c r="M368" t="s">
+        <v>229</v>
+      </c>
+      <c r="N368" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="369" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A369" t="s">
+        <v>783</v>
+      </c>
+      <c r="B369" t="s">
+        <v>785</v>
+      </c>
+      <c r="D369" t="s">
+        <v>29</v>
+      </c>
+      <c r="E369" t="s">
+        <v>408</v>
+      </c>
+      <c r="F369" t="s">
+        <v>17</v>
+      </c>
+      <c r="G369" t="s">
+        <v>8</v>
+      </c>
+      <c r="H369" t="s">
+        <v>403</v>
+      </c>
+      <c r="I369" t="s">
+        <v>9</v>
+      </c>
+      <c r="J369" t="s">
+        <v>9</v>
+      </c>
+      <c r="K369">
         <v>2001</v>
       </c>
+      <c r="L369" t="s">
+        <v>9</v>
+      </c>
+      <c r="M369" t="s">
+        <v>229</v>
+      </c>
+      <c r="N369" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="370" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A370" t="s">
+        <v>784</v>
+      </c>
+      <c r="B370" t="s">
+        <v>786</v>
+      </c>
+      <c r="D370" t="s">
+        <v>29</v>
+      </c>
+      <c r="E370" t="s">
+        <v>11</v>
+      </c>
+      <c r="F370" t="s">
+        <v>17</v>
+      </c>
+      <c r="G370" t="s">
+        <v>8</v>
+      </c>
+      <c r="H370" t="s">
+        <v>31</v>
+      </c>
+      <c r="I370" t="s">
+        <v>9</v>
+      </c>
+      <c r="J370" t="s">
+        <v>9</v>
+      </c>
+      <c r="K370">
+        <v>2001</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N368" xr:uid="{5694E675-77F6-4F54-A793-A54451BF0049}"/>
+  <autoFilter ref="A1:N370" xr:uid="{5694E675-77F6-4F54-A793-A54451BF0049}"/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Utilities/titles/VariableListing.xlsx
+++ b/Utilities/titles/VariableListing.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26731"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26924"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Work profile\Documents\GitHub\FTT_StandAlone\Utilities\titles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D02C101A-197E-421E-B5BF-F6988C5F41F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27FCA3B5-F3FA-4701-819A-9034AC1F39DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" xr2:uid="{3966A5EA-18B5-40FC-82B6-8DC341B5B05B}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3767" uniqueCount="811">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3793" uniqueCount="816">
   <si>
     <t>Variable name</t>
   </si>
@@ -2470,6 +2470,21 @@
   </si>
   <si>
     <t>Capacity by load band</t>
+  </si>
+  <si>
+    <t>relative_electricity_price</t>
+  </si>
+  <si>
+    <t>relative electricity price from start date FTT-P</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>MPRI</t>
+  </si>
+  <si>
+    <t>Switch for electricity price calculation (1=Double weighted LCOE, 2=Merit order approach)</t>
   </si>
 </sst>
 </file>
@@ -2844,7 +2859,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5694E675-77F6-4F54-A793-A54451BF0049}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:N370"/>
+  <dimension ref="A1:N372"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14" bestFit="1" customWidth="1"/>
@@ -14448,7 +14463,7 @@
         <v>29</v>
       </c>
       <c r="E324" t="s">
-        <v>17</v>
+        <v>199</v>
       </c>
       <c r="F324" t="s">
         <v>17</v>
@@ -16173,6 +16188,91 @@
       </c>
       <c r="K370">
         <v>2001</v>
+      </c>
+    </row>
+    <row r="371" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A371" t="s">
+        <v>811</v>
+      </c>
+      <c r="B371" t="s">
+        <v>812</v>
+      </c>
+      <c r="C371" t="s">
+        <v>260</v>
+      </c>
+      <c r="D371" t="s">
+        <v>29</v>
+      </c>
+      <c r="E371" t="s">
+        <v>17</v>
+      </c>
+      <c r="F371" t="s">
+        <v>17</v>
+      </c>
+      <c r="G371" t="s">
+        <v>8</v>
+      </c>
+      <c r="H371" t="s">
+        <v>31</v>
+      </c>
+      <c r="I371" t="s">
+        <v>9</v>
+      </c>
+      <c r="J371" t="s">
+        <v>9</v>
+      </c>
+      <c r="K371">
+        <v>2010</v>
+      </c>
+      <c r="L371" t="s">
+        <v>9</v>
+      </c>
+      <c r="M371" t="s">
+        <v>813</v>
+      </c>
+      <c r="N371" t="s">
+        <v>813</v>
+      </c>
+    </row>
+    <row r="372" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A372" t="s">
+        <v>814</v>
+      </c>
+      <c r="B372" t="s">
+        <v>815</v>
+      </c>
+      <c r="D372" t="s">
+        <v>17</v>
+      </c>
+      <c r="E372" t="s">
+        <v>17</v>
+      </c>
+      <c r="F372" t="s">
+        <v>17</v>
+      </c>
+      <c r="G372" t="s">
+        <v>17</v>
+      </c>
+      <c r="H372" t="s">
+        <v>31</v>
+      </c>
+      <c r="I372" t="s">
+        <v>9</v>
+      </c>
+      <c r="J372" t="s">
+        <v>9</v>
+      </c>
+      <c r="K372" t="s">
+        <v>9</v>
+      </c>
+      <c r="L372" t="s">
+        <v>9</v>
+      </c>
+      <c r="M372" t="s">
+        <v>813</v>
+      </c>
+      <c r="N372" t="s">
+        <v>813</v>
       </c>
     </row>
   </sheetData>

--- a/Utilities/titles/VariableListing.xlsx
+++ b/Utilities/titles/VariableListing.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Work profile\Documents\GitHub\FTT_StandAlone\Utilities\titles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27FCA3B5-F3FA-4701-819A-9034AC1F39DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCFA3DAC-E579-461C-ABF7-2A3D2C81F83F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" xr2:uid="{3966A5EA-18B5-40FC-82B6-8DC341B5B05B}"/>
   </bookViews>
@@ -16242,7 +16242,7 @@
         <v>815</v>
       </c>
       <c r="D372" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="E372" t="s">
         <v>17</v>
